--- a/files/九龙-西南九龙-叡璟II.xlsx
+++ b/files/九龙-西南九龙-叡璟II.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,6 +122,12 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <color rgb="00002060"/>
       <sz val="8"/>
     </font>
@@ -196,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -258,7 +264,10 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1100,7 +1109,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1108,34 +1117,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H8" s="5" t="n">
+        <v>11883000</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>25889</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>9981720</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>21747</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1240,7 +1241,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1250,12 +1251,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1265,12 +1266,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1280,7 +1281,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1451,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1458,34 +1459,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H13" s="5" t="n">
+        <v>11696000</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>25481</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>9824640</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>21404</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1590,7 +1583,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1600,12 +1593,12 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1615,12 +1608,12 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1630,7 +1623,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1793,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1808,34 +1801,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H18" s="5" t="n">
+        <v>11377000</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>24786</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>9556680</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>20821</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -1940,7 +1925,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1950,12 +1935,12 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1965,12 +1950,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -1980,7 +1965,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2135,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2158,34 +2143,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H23" s="5" t="n">
+        <v>11265000</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>24542</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>9462600</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>20616</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -2290,7 +2267,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2300,12 +2277,12 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2315,12 +2292,12 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -2330,7 +2307,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2477,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -2508,34 +2485,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H28" s="5" t="n">
+        <v>11153000</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>24298</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>9368520</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>20411</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -2640,7 +2609,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -2650,12 +2619,12 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -2665,12 +2634,12 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -2680,7 +2649,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2819,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2858,34 +2827,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H33" s="5" t="n">
+        <v>11043000</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>24059</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>9276120</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>20209</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -2990,7 +2951,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -3000,12 +2961,12 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -3015,12 +2976,12 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -3030,7 +2991,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3223,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -3270,34 +3231,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H39" s="5" t="n">
+        <v>11153000</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>24193</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>9368520</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>20322</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -3332,7 +3285,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -3342,12 +3295,12 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -3357,12 +3310,12 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -3372,7 +3325,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3557,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -3612,34 +3565,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H44" s="5" t="n">
+        <v>11021000</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>23907</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>9257640</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>20082</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -3674,7 +3619,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -3684,12 +3629,12 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -3699,12 +3644,12 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -3714,7 +3659,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3946,7 +3891,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -3954,34 +3899,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H49" s="5" t="n">
+        <v>10977000</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>23811</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>9220680</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>20001</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
@@ -4016,7 +3953,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -4026,12 +3963,12 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -4041,12 +3978,12 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -4056,7 +3993,7 @@
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4225,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -4296,34 +4233,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H54" s="5" t="n">
+        <v>10933000</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>23716</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>9183720</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>19921</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -4358,7 +4287,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -4368,12 +4297,12 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -4383,12 +4312,12 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -4398,7 +4327,7 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4559,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -4638,34 +4567,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H59" s="5" t="n">
+        <v>10889000</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>23620</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K59" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L59" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>9146760</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>19841</v>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
@@ -4700,7 +4621,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -4710,12 +4631,12 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -4725,12 +4646,12 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -4740,7 +4661,7 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4893,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -4980,34 +4901,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H64" s="5" t="n">
+        <v>10846000</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>23527</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>9110640</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>19763</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
@@ -5042,7 +4955,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -5052,12 +4965,12 @@
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
@@ -5067,12 +4980,12 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
@@ -5082,7 +4995,7 @@
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5227,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -5322,34 +5235,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H69" s="5" t="n">
+        <v>10803000</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>23434</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>9074520</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>19684</v>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
@@ -5384,7 +5289,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -5394,12 +5299,12 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
@@ -5409,12 +5314,12 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
@@ -5424,7 +5329,7 @@
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5561,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -5664,34 +5569,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H74" s="5" t="n">
+        <v>10760000</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>23341</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>9038400</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>19606</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -5726,7 +5623,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -5736,12 +5633,12 @@
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
@@ -5751,12 +5648,12 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
@@ -5766,7 +5663,7 @@
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5895,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -6006,34 +5903,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H79" s="5" t="n">
+        <v>10717000</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>23247</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K79" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L79" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>9002280</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>19528</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
@@ -6068,7 +5957,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -6078,12 +5967,12 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
@@ -6093,12 +5982,12 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -6108,7 +5997,7 @@
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6340,7 +6229,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -6348,34 +6237,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H84" s="5" t="n">
+        <v>10717000</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>23247</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K84" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L84" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>9002280</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>19528</v>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
@@ -6410,7 +6291,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -6420,12 +6301,12 @@
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
@@ -6435,12 +6316,12 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
@@ -6450,7 +6331,7 @@
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6563,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
@@ -6690,34 +6571,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I89" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H89" s="5" t="n">
+        <v>10632000</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>23063</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K89" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L89" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>8930880</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>19373</v>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
@@ -6752,7 +6625,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
@@ -6762,12 +6635,12 @@
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J90" s="3" t="inlineStr">
@@ -6777,12 +6650,12 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
@@ -6792,7 +6665,7 @@
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7024,7 +6897,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -7032,34 +6905,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I94" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H94" s="5" t="n">
+        <v>10414000</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>22590</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K94" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L94" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>8747760</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>18976</v>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
@@ -7164,7 +7029,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -7172,34 +7037,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I96" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H96" s="5" t="n">
+        <v>17866000</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>24474</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K96" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L96" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>15007440</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>20558</v>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
@@ -7234,7 +7091,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -7242,34 +7099,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I97" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H97" s="5" t="n">
+        <v>17732000</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>24526</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L97" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>14894880</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>20601</v>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N97" s="3" t="inlineStr">
@@ -7366,7 +7215,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -7374,34 +7223,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I99" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H99" s="5" t="n">
+        <v>10383000</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>22523</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L99" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>8721720</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>18919</v>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N99" s="3" t="inlineStr">
@@ -7506,7 +7347,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -7514,34 +7355,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H101" s="5" t="n">
+        <v>17654000</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>24184</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>14829360</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>20314</v>
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N101" s="3" t="inlineStr">
@@ -7576,7 +7409,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -7584,34 +7417,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H102" s="5" t="n">
+        <v>17522000</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>24235</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K102" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L102" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>14718480</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>20358</v>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N102" s="3" t="inlineStr">
@@ -7708,7 +7533,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -7716,34 +7541,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I104" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H104" s="5" t="n">
+        <v>10352000</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>22456</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K104" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L104" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>8695680</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>18863</v>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N104" s="3" t="inlineStr">
@@ -7848,7 +7665,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -7856,34 +7673,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I106" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H106" s="5" t="n">
+        <v>17445000</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>23897</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K106" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L106" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>14653800</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>20074</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N106" s="3" t="inlineStr">
@@ -7918,7 +7727,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -7926,34 +7735,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I107" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H107" s="5" t="n">
+        <v>17314000</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>23947</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K107" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L107" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>14543760</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>20116</v>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N107" s="3" t="inlineStr">
@@ -7988,7 +7789,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -7996,34 +7797,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I108" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H108" s="5" t="n">
+        <v>10248000</v>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>22278</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K108" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L108" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>8608320</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>18714</v>
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N108" s="3" t="inlineStr">
@@ -8190,7 +7983,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -8198,34 +7991,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I111" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H111" s="5" t="n">
+        <v>17238000</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>23614</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K111" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L111" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>14479920</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>19836</v>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N111" s="3" t="inlineStr">
@@ -8260,7 +8045,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -8268,34 +8053,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I112" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H112" s="5" t="n">
+        <v>17109000</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>23664</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K112" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L112" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>14371560</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>19878</v>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N112" s="3" t="inlineStr">
@@ -8330,7 +8107,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -8338,34 +8115,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H113" s="5" t="n">
+        <v>10218000</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>22213</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>8583120</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>18659</v>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N113" s="3" t="inlineStr">
@@ -8532,7 +8301,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
@@ -8540,34 +8309,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I116" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H116" s="5" t="n">
+        <v>17034000</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>23334</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K116" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L116" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>14308560</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>19601</v>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N116" s="3" t="inlineStr">
@@ -8602,7 +8363,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
@@ -8610,34 +8371,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H117" s="5" t="n">
+        <v>16906000</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>23383</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>14201040</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>19642</v>
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N117" s="3" t="inlineStr">
@@ -8672,7 +8425,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -8680,34 +8433,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H118" s="5" t="n">
+        <v>10187000</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>22146</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>8557080</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>18602</v>
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N118" s="3" t="inlineStr">
@@ -9060,7 +8805,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -9068,34 +8813,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H124" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I124" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H124" s="5" t="n">
+        <v>10259000</v>
+      </c>
+      <c r="I124" s="5" t="n">
+        <v>22254</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K124" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L124" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>8617560</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>18693</v>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N124" s="3" t="inlineStr">
@@ -9386,7 +9123,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
@@ -9394,34 +9131,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H129" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I129" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H129" s="5" t="n">
+        <v>10197000</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>22119</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K129" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L129" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>8565480</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>18580</v>
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N129" s="3" t="inlineStr">
@@ -9712,7 +9441,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
@@ -9720,34 +9449,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I134" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H134" s="5" t="n">
+        <v>10167000</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>22054</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K134" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L134" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>8540280</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>18526</v>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N134" s="3" t="inlineStr">
@@ -9976,7 +9697,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -9984,34 +9705,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I138" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H138" s="5" t="n">
+        <v>10065000</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>21880</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K138" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L138" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>8454600</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>18380</v>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N138" s="3" t="inlineStr">
@@ -10302,7 +10015,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
@@ -10310,34 +10023,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H143" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I143" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H143" s="5" t="n">
+        <v>10035000</v>
+      </c>
+      <c r="I143" s="5" t="n">
+        <v>21815</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K143" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L143" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>8429400</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>18325</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N143" s="3" t="inlineStr">
@@ -10628,7 +10333,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
@@ -10636,34 +10341,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H148" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I148" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H148" s="5" t="n">
+        <v>10005000</v>
+      </c>
+      <c r="I148" s="5" t="n">
+        <v>21750</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K148" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L148" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>8404200</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>18270</v>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N148" s="3" t="inlineStr">
@@ -11016,7 +10713,7 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
@@ -11024,34 +10721,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I154" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H154" s="5" t="n">
+        <v>10045000</v>
+      </c>
+      <c r="I154" s="5" t="n">
+        <v>21790</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K154" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L154" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>8437800</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>18303</v>
       </c>
       <c r="M154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N154" s="3" t="inlineStr">
@@ -11342,7 +11031,7 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -11350,34 +11039,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H159" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I159" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H159" s="5" t="n">
+        <v>10015000</v>
+      </c>
+      <c r="I159" s="5" t="n">
+        <v>21725</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K159" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L159" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>8412600</v>
+      </c>
+      <c r="L159" s="5" t="n">
+        <v>18249</v>
       </c>
       <c r="M159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N159" s="3" t="inlineStr">
@@ -11668,7 +11349,7 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -11676,34 +11357,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I164" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H164" s="5" t="n">
+        <v>10015000</v>
+      </c>
+      <c r="I164" s="5" t="n">
+        <v>21725</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K164" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L164" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>8412600</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>18249</v>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N164" s="3" t="inlineStr">
@@ -11932,7 +11605,7 @@
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
@@ -11940,34 +11613,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H168" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I168" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H168" s="5" t="n">
+        <v>9885000</v>
+      </c>
+      <c r="I168" s="5" t="n">
+        <v>21489</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K168" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L168" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>8303400</v>
+      </c>
+      <c r="L168" s="5" t="n">
+        <v>18051</v>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N168" s="3" t="inlineStr">
@@ -12258,7 +11923,7 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -12266,34 +11931,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H173" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I173" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H173" s="5" t="n">
+        <v>9856000</v>
+      </c>
+      <c r="I173" s="5" t="n">
+        <v>21426</v>
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L173" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K173" s="5" t="n">
+        <v>8279040</v>
+      </c>
+      <c r="L173" s="5" t="n">
+        <v>17998</v>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N173" s="3" t="inlineStr">
@@ -12584,7 +12241,7 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -12592,34 +12249,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H178" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I178" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H178" s="5" t="n">
+        <v>9796000</v>
+      </c>
+      <c r="I178" s="5" t="n">
+        <v>21296</v>
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K178" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L178" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>8228640</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>17888</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N178" s="3" t="inlineStr">
@@ -12910,7 +12559,7 @@
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
@@ -12920,12 +12569,12 @@
       </c>
       <c r="H183" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I183" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J183" s="3" t="inlineStr">
@@ -12935,12 +12584,12 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L183" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M183" s="3" t="inlineStr">
@@ -12950,7 +12599,7 @@
       </c>
       <c r="N183" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12629,7 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
@@ -12990,12 +12639,12 @@
       </c>
       <c r="H184" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I184" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J184" s="3" t="inlineStr">
@@ -13005,12 +12654,12 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M184" s="3" t="inlineStr">
@@ -13020,7 +12669,7 @@
       </c>
       <c r="N184" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13050,7 +12699,7 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
@@ -13060,12 +12709,12 @@
       </c>
       <c r="H185" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I185" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J185" s="3" t="inlineStr">
@@ -13075,12 +12724,12 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L185" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M185" s="3" t="inlineStr">
@@ -13090,7 +12739,7 @@
       </c>
       <c r="N185" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13120,7 +12769,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -13130,12 +12779,12 @@
       </c>
       <c r="H186" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I186" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J186" s="3" t="inlineStr">
@@ -13145,12 +12794,12 @@
       </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L186" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M186" s="3" t="inlineStr">
@@ -13160,7 +12809,7 @@
       </c>
       <c r="N186" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -15150,7 +14799,7 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -15158,34 +14807,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H215" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I215" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H215" s="5" t="n">
+        <v>7602000</v>
+      </c>
+      <c r="I215" s="5" t="n">
+        <v>23609</v>
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K215" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L215" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K215" s="5" t="n">
+        <v>6385680</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>19831</v>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N215" s="3" t="inlineStr">
@@ -15570,7 +15211,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -15578,34 +15219,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H221" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I221" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H221" s="5" t="n">
+        <v>7526000</v>
+      </c>
+      <c r="I221" s="5" t="n">
+        <v>23373</v>
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K221" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L221" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K221" s="5" t="n">
+        <v>6321840</v>
+      </c>
+      <c r="L221" s="5" t="n">
+        <v>19633</v>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
@@ -15990,7 +15623,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -15998,34 +15631,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H227" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I227" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H227" s="5" t="n">
+        <v>7452000</v>
+      </c>
+      <c r="I227" s="5" t="n">
+        <v>23143</v>
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K227" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L227" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K227" s="5" t="n">
+        <v>6259680</v>
+      </c>
+      <c r="L227" s="5" t="n">
+        <v>19440</v>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N227" s="3" t="inlineStr">
@@ -16410,7 +16035,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -16418,34 +16043,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H233" s="5" t="n">
+        <v>7452000</v>
+      </c>
+      <c r="I233" s="5" t="n">
+        <v>23143</v>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>6259680</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>19440</v>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N233" s="3" t="inlineStr">
@@ -16550,7 +16167,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -16560,12 +16177,12 @@
       </c>
       <c r="H235" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I235" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J235" s="3" t="inlineStr">
@@ -16575,12 +16192,12 @@
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L235" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M235" s="3" t="inlineStr">
@@ -16590,7 +16207,7 @@
       </c>
       <c r="N235" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -16830,7 +16447,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -16838,34 +16455,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H239" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I239" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H239" s="5" t="n">
+        <v>7407000</v>
+      </c>
+      <c r="I239" s="5" t="n">
+        <v>23003</v>
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K239" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L239" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K239" s="5" t="n">
+        <v>6221880</v>
+      </c>
+      <c r="L239" s="5" t="n">
+        <v>19323</v>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N239" s="3" t="inlineStr">
@@ -16970,7 +16579,7 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -16980,12 +16589,12 @@
       </c>
       <c r="H241" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I241" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J241" s="3" t="inlineStr">
@@ -16995,12 +16604,12 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L241" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M241" s="3" t="inlineStr">
@@ -17010,7 +16619,7 @@
       </c>
       <c r="N241" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -17040,7 +16649,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -17048,34 +16657,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H242" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I242" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H242" s="5" t="n">
+        <v>9500000</v>
+      </c>
+      <c r="I242" s="5" t="n">
+        <v>23058</v>
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K242" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L242" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K242" s="5" t="n">
+        <v>7980000</v>
+      </c>
+      <c r="L242" s="5" t="n">
+        <v>19369</v>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N242" s="3" t="inlineStr">
@@ -17250,7 +16851,7 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -17258,34 +16859,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H245" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I245" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H245" s="5" t="n">
+        <v>7385000</v>
+      </c>
+      <c r="I245" s="5" t="n">
+        <v>22935</v>
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K245" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L245" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K245" s="5" t="n">
+        <v>6203400</v>
+      </c>
+      <c r="L245" s="5" t="n">
+        <v>19265</v>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N245" s="3" t="inlineStr">
@@ -17390,7 +16983,7 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -17400,12 +16993,12 @@
       </c>
       <c r="H247" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I247" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J247" s="3" t="inlineStr">
@@ -17415,12 +17008,12 @@
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L247" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M247" s="3" t="inlineStr">
@@ -17430,7 +17023,7 @@
       </c>
       <c r="N247" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -17460,7 +17053,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -17468,34 +17061,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H248" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I248" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H248" s="5" t="n">
+        <v>9406000</v>
+      </c>
+      <c r="I248" s="5" t="n">
+        <v>22830</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K248" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L248" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K248" s="5" t="n">
+        <v>7901040</v>
+      </c>
+      <c r="L248" s="5" t="n">
+        <v>19177</v>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N248" s="3" t="inlineStr">
@@ -17670,7 +17255,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -17678,34 +17263,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H251" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I251" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H251" s="5" t="n">
+        <v>7363000</v>
+      </c>
+      <c r="I251" s="5" t="n">
+        <v>22866</v>
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K251" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L251" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K251" s="5" t="n">
+        <v>6184920</v>
+      </c>
+      <c r="L251" s="5" t="n">
+        <v>19208</v>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N251" s="3" t="inlineStr">
@@ -17810,7 +17387,7 @@
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -17820,12 +17397,12 @@
       </c>
       <c r="H253" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I253" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J253" s="3" t="inlineStr">
@@ -17835,12 +17412,12 @@
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L253" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M253" s="3" t="inlineStr">
@@ -17850,7 +17427,7 @@
       </c>
       <c r="N253" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -17880,7 +17457,7 @@
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -17888,34 +17465,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H254" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I254" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H254" s="5" t="n">
+        <v>9312000</v>
+      </c>
+      <c r="I254" s="5" t="n">
+        <v>22602</v>
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K254" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L254" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K254" s="5" t="n">
+        <v>7822080</v>
+      </c>
+      <c r="L254" s="5" t="n">
+        <v>18986</v>
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N254" s="3" t="inlineStr">
@@ -18090,7 +17659,7 @@
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -18098,34 +17667,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H257" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I257" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H257" s="5" t="n">
+        <v>7341000</v>
+      </c>
+      <c r="I257" s="5" t="n">
+        <v>22798</v>
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K257" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L257" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K257" s="5" t="n">
+        <v>6166440</v>
+      </c>
+      <c r="L257" s="5" t="n">
+        <v>19150</v>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N257" s="3" t="inlineStr">
@@ -18230,7 +17791,7 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -18240,12 +17801,12 @@
       </c>
       <c r="H259" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I259" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J259" s="3" t="inlineStr">
@@ -18255,12 +17816,12 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L259" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M259" s="3" t="inlineStr">
@@ -18270,7 +17831,7 @@
       </c>
       <c r="N259" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18502,7 +18063,7 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -18510,34 +18071,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H263" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I263" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H263" s="5" t="n">
+        <v>7319000</v>
+      </c>
+      <c r="I263" s="5" t="n">
+        <v>22730</v>
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K263" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L263" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K263" s="5" t="n">
+        <v>6147960</v>
+      </c>
+      <c r="L263" s="5" t="n">
+        <v>19093</v>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N263" s="3" t="inlineStr">
@@ -18642,7 +18195,7 @@
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -18652,12 +18205,12 @@
       </c>
       <c r="H265" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I265" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J265" s="3" t="inlineStr">
@@ -18667,12 +18220,12 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L265" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M265" s="3" t="inlineStr">
@@ -18682,7 +18235,7 @@
       </c>
       <c r="N265" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18914,7 +18467,7 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -18922,34 +18475,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H269" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I269" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H269" s="5" t="n">
+        <v>7297000</v>
+      </c>
+      <c r="I269" s="5" t="n">
+        <v>22661</v>
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K269" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L269" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K269" s="5" t="n">
+        <v>6129480</v>
+      </c>
+      <c r="L269" s="5" t="n">
+        <v>19036</v>
       </c>
       <c r="M269" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N269" s="3" t="inlineStr">
@@ -19054,7 +18599,7 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -19064,12 +18609,12 @@
       </c>
       <c r="H271" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I271" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J271" s="3" t="inlineStr">
@@ -19079,12 +18624,12 @@
       </c>
       <c r="K271" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L271" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M271" s="3" t="inlineStr">
@@ -19094,7 +18639,7 @@
       </c>
       <c r="N271" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19326,7 +18871,7 @@
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -19334,34 +18879,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H275" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I275" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H275" s="5" t="n">
+        <v>7275000</v>
+      </c>
+      <c r="I275" s="5" t="n">
+        <v>22593</v>
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K275" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L275" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K275" s="5" t="n">
+        <v>6111000</v>
+      </c>
+      <c r="L275" s="5" t="n">
+        <v>18978</v>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N275" s="3" t="inlineStr">
@@ -19466,7 +19003,7 @@
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -19476,12 +19013,12 @@
       </c>
       <c r="H277" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I277" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J277" s="3" t="inlineStr">
@@ -19491,12 +19028,12 @@
       </c>
       <c r="K277" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L277" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M277" s="3" t="inlineStr">
@@ -19506,7 +19043,7 @@
       </c>
       <c r="N277" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19536,7 +19073,7 @@
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -19544,34 +19081,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H278" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I278" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H278" s="5" t="n">
+        <v>9138000</v>
+      </c>
+      <c r="I278" s="5" t="n">
+        <v>22180</v>
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K278" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L278" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K278" s="5" t="n">
+        <v>7675920</v>
+      </c>
+      <c r="L278" s="5" t="n">
+        <v>18631</v>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N278" s="3" t="inlineStr">
@@ -19746,7 +19275,7 @@
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -19754,34 +19283,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H281" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I281" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H281" s="5" t="n">
+        <v>7254000</v>
+      </c>
+      <c r="I281" s="5" t="n">
+        <v>22528</v>
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K281" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L281" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K281" s="5" t="n">
+        <v>6093360</v>
+      </c>
+      <c r="L281" s="5" t="n">
+        <v>18923</v>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N281" s="3" t="inlineStr">
@@ -19886,7 +19407,7 @@
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -19896,12 +19417,12 @@
       </c>
       <c r="H283" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I283" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J283" s="3" t="inlineStr">
@@ -19911,12 +19432,12 @@
       </c>
       <c r="K283" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L283" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M283" s="3" t="inlineStr">
@@ -19926,7 +19447,7 @@
       </c>
       <c r="N283" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19956,7 +19477,7 @@
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -19964,34 +19485,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H284" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I284" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H284" s="5" t="n">
+        <v>9138000</v>
+      </c>
+      <c r="I284" s="5" t="n">
+        <v>22180</v>
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K284" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L284" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K284" s="5" t="n">
+        <v>7675920</v>
+      </c>
+      <c r="L284" s="5" t="n">
+        <v>18631</v>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N284" s="3" t="inlineStr">
@@ -20166,7 +19679,7 @@
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -20174,34 +19687,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H287" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I287" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H287" s="5" t="n">
+        <v>7254000</v>
+      </c>
+      <c r="I287" s="5" t="n">
+        <v>22528</v>
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K287" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L287" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K287" s="5" t="n">
+        <v>6093360</v>
+      </c>
+      <c r="L287" s="5" t="n">
+        <v>18923</v>
       </c>
       <c r="M287" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N287" s="3" t="inlineStr">
@@ -20306,7 +19811,7 @@
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -20316,12 +19821,12 @@
       </c>
       <c r="H289" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I289" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J289" s="3" t="inlineStr">
@@ -20331,12 +19836,12 @@
       </c>
       <c r="K289" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L289" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M289" s="3" t="inlineStr">
@@ -20346,7 +19851,7 @@
       </c>
       <c r="N289" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -20376,7 +19881,7 @@
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -20384,34 +19889,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H290" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I290" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H290" s="5" t="n">
+        <v>9083000</v>
+      </c>
+      <c r="I290" s="5" t="n">
+        <v>22046</v>
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K290" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L290" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K290" s="5" t="n">
+        <v>7629720</v>
+      </c>
+      <c r="L290" s="5" t="n">
+        <v>18519</v>
       </c>
       <c r="M290" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N290" s="3" t="inlineStr">
@@ -20586,7 +20083,7 @@
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
@@ -20594,34 +20091,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H293" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I293" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H293" s="5" t="n">
+        <v>7138000</v>
+      </c>
+      <c r="I293" s="5" t="n">
+        <v>22168</v>
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K293" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L293" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K293" s="5" t="n">
+        <v>5995920</v>
+      </c>
+      <c r="L293" s="5" t="n">
+        <v>18621</v>
       </c>
       <c r="M293" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N293" s="3" t="inlineStr">
@@ -20726,7 +20215,7 @@
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -20736,12 +20225,12 @@
       </c>
       <c r="H295" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I295" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J295" s="3" t="inlineStr">
@@ -20751,12 +20240,12 @@
       </c>
       <c r="K295" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L295" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M295" s="3" t="inlineStr">
@@ -20766,7 +20255,7 @@
       </c>
       <c r="N295" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -25716,7 +25205,7 @@
       </c>
       <c r="F368" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G368" s="3" t="inlineStr">
@@ -25724,34 +25213,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H368" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I368" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H368" s="5" t="n">
+        <v>8800000</v>
+      </c>
+      <c r="I368" s="5" t="n">
+        <v>21308</v>
       </c>
       <c r="J368" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K368" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L368" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K368" s="5" t="n">
+        <v>7392000</v>
+      </c>
+      <c r="L368" s="5" t="n">
+        <v>17898</v>
       </c>
       <c r="M368" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N368" s="3" t="inlineStr">
@@ -26128,7 +25609,7 @@
       </c>
       <c r="F374" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G374" s="3" t="inlineStr">
@@ -26136,34 +25617,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H374" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I374" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H374" s="5" t="n">
+        <v>8783000</v>
+      </c>
+      <c r="I374" s="5" t="n">
+        <v>21266</v>
       </c>
       <c r="J374" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K374" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L374" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K374" s="5" t="n">
+        <v>7377720</v>
+      </c>
+      <c r="L374" s="5" t="n">
+        <v>17864</v>
       </c>
       <c r="M374" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N374" s="3" t="inlineStr">
@@ -26540,7 +26013,7 @@
       </c>
       <c r="F380" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G380" s="3" t="inlineStr">
@@ -26548,34 +26021,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H380" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I380" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H380" s="5" t="n">
+        <v>8783000</v>
+      </c>
+      <c r="I380" s="5" t="n">
+        <v>21266</v>
       </c>
       <c r="J380" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K380" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L380" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K380" s="5" t="n">
+        <v>7377720</v>
+      </c>
+      <c r="L380" s="5" t="n">
+        <v>17864</v>
       </c>
       <c r="M380" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N380" s="3" t="inlineStr">
@@ -28140,7 +27605,7 @@
       </c>
       <c r="F404" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G404" s="3" t="inlineStr">
@@ -28150,12 +27615,12 @@
       </c>
       <c r="H404" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I404" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J404" s="3" t="inlineStr">
@@ -28165,12 +27630,12 @@
       </c>
       <c r="K404" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L404" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M404" s="3" t="inlineStr">
@@ -28180,7 +27645,7 @@
       </c>
       <c r="N404" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -28420,7 +27885,7 @@
       </c>
       <c r="F408" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G408" s="3" t="inlineStr">
@@ -28430,12 +27895,12 @@
       </c>
       <c r="H408" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I408" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J408" s="3" t="inlineStr">
@@ -28445,12 +27910,12 @@
       </c>
       <c r="K408" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L408" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M408" s="3" t="inlineStr">
@@ -28460,7 +27925,7 @@
       </c>
       <c r="N408" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -28490,7 +27955,7 @@
       </c>
       <c r="F409" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G409" s="3" t="inlineStr">
@@ -28500,12 +27965,12 @@
       </c>
       <c r="H409" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I409" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J409" s="3" t="inlineStr">
@@ -28515,12 +27980,12 @@
       </c>
       <c r="K409" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L409" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M409" s="3" t="inlineStr">
@@ -28530,7 +27995,7 @@
       </c>
       <c r="N409" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -28607,27 +28072,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>64</t>
         </is>
       </c>
     </row>
@@ -28732,28 +28197,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 461呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
-        <is>
-          <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
--
--
-(待售)</t>
+$1188万
+$25,889/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -28779,28 +28244,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 461呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
--
--
-(待售)</t>
+$1170万
+$25,481/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -28826,28 +28291,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 461呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
--
--
-(待售)</t>
+$1138万
+$24,786/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -28873,28 +28338,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 461呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
--
--
-(待售)</t>
+$1126万
+$24,542/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -28920,28 +28385,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 461呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
--
--
-(待售)</t>
+$1115万
+$24,298/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -28967,28 +28432,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 461呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
--
--
-(待售)</t>
+$1104万
+$24,059/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -29014,23 +28479,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
+$1115万
+$24,193/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1093万
@@ -29061,23 +28526,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
+$1102万
+$23,907/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1080万
@@ -29108,23 +28573,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="inlineStr">
+$1098万
+$23,811/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1076万
@@ -29155,23 +28620,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="21" t="inlineStr">
+$1093万
+$23,716/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1072万
@@ -29202,23 +28667,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
+$1089万
+$23,620/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1068万
@@ -29249,23 +28714,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
+$1085万
+$23,527/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1063万
@@ -29296,23 +28761,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
+$1080万
+$23,434/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1059万
@@ -29343,23 +28808,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
+$1076万
+$23,341/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1055万
@@ -29390,23 +28855,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
+$1072万
+$23,247/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1051万
@@ -29437,23 +28902,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="21" t="inlineStr">
+$1072万
+$23,247/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1051万
@@ -29484,23 +28949,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
+$1063万
+$23,063/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1042万
@@ -29515,39 +28980,39 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
+$1773万
+$24,526/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 730呎 (3房)
+$1787万
+$24,474/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 714呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>B | 730呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>C | 714呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="inlineStr">
+$1041万
+$22,590/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $1034万
@@ -29562,39 +29027,39 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
+$1752万
+$24,235/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 730呎 (3房)
+$1765万
+$24,184/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 714呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>B | 730呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>C | 714呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
+$1038万
+$22,523/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $1031万
@@ -29609,39 +29074,39 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
+$1731万
+$23,947/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 730呎 (3房)
+$1744万
+$23,897/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 714呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>B | 730呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="20" t="inlineStr">
-        <is>
-          <t>C | 714呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
+$1035万
+$22,456/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $1028万
@@ -29656,31 +29121,31 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
+$1711万
+$23,664/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 730呎 (3房)
+$1724万
+$23,614/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 714呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>B | 730呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>C | 714呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1032万
@@ -29688,12 +29153,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F26" s="20" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
--
--
-(待售)</t>
+$1025万
+$22,278/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -29703,31 +29168,31 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
+$1691万
+$23,383/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 730呎 (3房)
+$1703万
+$23,334/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 714呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
-        <is>
-          <t>B | 730呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="20" t="inlineStr">
-        <is>
-          <t>C | 714呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1029万
@@ -29735,12 +29200,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
--
--
-(待售)</t>
+$1022万
+$22,213/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -29750,7 +29215,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1671万
@@ -29758,7 +29223,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1683万
@@ -29774,7 +29239,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1026万
@@ -29782,12 +29247,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
--
--
-(待售)</t>
+$1019万
+$22,146/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -29797,7 +29262,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1671万
@@ -29805,7 +29270,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1683万
@@ -29821,15 +29286,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="21" t="inlineStr">
+$1026万
+$22,254/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $1019万
@@ -29844,7 +29309,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1657万
@@ -29852,7 +29317,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1670万
@@ -29868,15 +29333,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F30" s="21" t="inlineStr">
+$1020万
+$22,119/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $1013万
@@ -29891,7 +29356,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1651万
@@ -29899,7 +29364,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1663万
@@ -29915,15 +29380,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E31" s="20" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F31" s="21" t="inlineStr">
+$1017万
+$22,054/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $1010万
@@ -29938,7 +29403,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1644万
@@ -29946,7 +29411,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1656万
@@ -29962,7 +29427,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E32" s="21" t="inlineStr">
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1014万
@@ -29970,12 +29435,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F32" s="20" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
--
--
-(待售)</t>
+$1006万
+$21,880/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -29985,7 +29450,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1637万
@@ -29993,7 +29458,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1650万
@@ -30009,7 +29474,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E33" s="21" t="inlineStr">
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1011万
@@ -30017,12 +29482,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F33" s="20" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
--
--
-(待售)</t>
+$1004万
+$21,815/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -30032,7 +29497,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1631万
@@ -30040,7 +29505,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1643万
@@ -30056,7 +29521,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E34" s="21" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1008万
@@ -30064,12 +29529,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F34" s="20" t="inlineStr">
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
--
--
-(待售)</t>
+$1000万
+$21,750/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -30079,7 +29544,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1624万
@@ -30087,7 +29552,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C35" s="21" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1637万
@@ -30103,15 +29568,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E35" s="20" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F35" s="21" t="inlineStr">
+$1004万
+$21,790/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $998万
@@ -30126,7 +29591,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1618万
@@ -30134,7 +29599,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1630万
@@ -30150,15 +29615,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E36" s="20" t="inlineStr">
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F36" s="21" t="inlineStr">
+$1002万
+$21,725/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $994万
@@ -30173,7 +29638,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1618万
@@ -30181,7 +29646,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1630万
@@ -30197,15 +29662,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E37" s="20" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F37" s="21" t="inlineStr">
+$1002万
+$21,725/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $994万
@@ -30220,7 +29685,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B38" s="21" t="inlineStr">
+      <c r="B38" s="22" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1605万
@@ -30228,7 +29693,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1617万
@@ -30244,7 +29709,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E38" s="21" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $996万
@@ -30252,12 +29717,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F38" s="20" t="inlineStr">
+      <c r="F38" s="22" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
--
--
-(待售)</t>
+$988万
+$21,489/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -30267,7 +29732,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B39" s="21" t="inlineStr">
+      <c r="B39" s="22" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1598万
@@ -30275,7 +29740,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C39" s="21" t="inlineStr">
+      <c r="C39" s="22" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1610万
@@ -30291,7 +29756,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E39" s="21" t="inlineStr">
+      <c r="E39" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $992万
@@ -30299,12 +29764,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F39" s="20" t="inlineStr">
+      <c r="F39" s="22" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
--
--
-(待售)</t>
+$986万
+$21,426/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -30314,7 +29779,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B40" s="21" t="inlineStr">
+      <c r="B40" s="22" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1592万
@@ -30322,7 +29787,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C40" s="21" t="inlineStr">
+      <c r="C40" s="22" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1604万
@@ -30338,7 +29803,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E40" s="21" t="inlineStr">
+      <c r="E40" s="22" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $987万
@@ -30346,12 +29811,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F40" s="20" t="inlineStr">
+      <c r="F40" s="22" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
--
--
-(待售)</t>
+$980万
+$21,296/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -30369,36 +29834,36 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C41" s="20" t="inlineStr">
+      <c r="C41" s="21" t="inlineStr">
         <is>
           <t>B | 686呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D41" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
         <is>
           <t>C | 676呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E41" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="inlineStr">
         <is>
           <t>D | 424呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F41" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
         <is>
           <t>E | 423呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -30476,27 +29941,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>155</t>
         </is>
       </c>
     </row>
@@ -30779,12 +30244,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 322呎 (1房)
--
--
-(待售)</t>
+$760万
+$23,609/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -30834,12 +30299,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 322呎 (1房)
--
--
-(待售)</t>
+$753万
+$23,373/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -30889,12 +30354,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 322呎 (1房)
--
--
-(待售)</t>
+$745万
+$23,143/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -30928,28 +30393,28 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>B | 447呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 322呎 (1房)
--
--
-(待售)</t>
+$745万
+$23,143/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -30983,28 +30448,28 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>B | 447呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 322呎 (1房)
--
--
-(待售)</t>
+$741万
+$23,003/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -31038,52 +30503,52 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>B | 447呎 (2房)
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 322呎 (1房)
+$738万
+$22,935/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 306呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>C | 322呎 (1房)
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 306呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
-        <is>
-          <t>D | 306呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>E | 306呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>F | 412呎 (2房)
--
--
-(待售)</t>
+$950万
+$23,058/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -31093,52 +30558,52 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>B | 447呎 (2房)
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 322呎 (1房)
+$736万
+$22,866/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 306呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>C | 322呎 (1房)
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 306呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
-        <is>
-          <t>D | 306呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>E | 306呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="20" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>F | 412呎 (2房)
--
--
-(待售)</t>
+$941万
+$22,830/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -31148,52 +30613,52 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>B | 447呎 (2房)
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 322呎 (1房)
+$734万
+$22,798/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 306呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>C | 322呎 (1房)
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 306呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>D | 306呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>E | 306呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>F | 412呎 (2房)
--
--
-(待售)</t>
+$931万
+$22,602/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -31203,47 +30668,47 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>B | 447呎 (2房)
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 322呎 (1房)
+$732万
+$22,730/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 306呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>C | 322呎 (1房)
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 306呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>D | 306呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>E | 306呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>F | 412呎 (2房)
 $922万
@@ -31258,47 +30723,47 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>B | 447呎 (2房)
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 322呎 (1房)
+$730万
+$22,661/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 306呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>C | 322呎 (1房)
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 306呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
-        <is>
-          <t>D | 306呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="20" t="inlineStr">
-        <is>
-          <t>E | 306呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>F | 412呎 (2房)
 $919万
@@ -31313,47 +30778,47 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>B | 447呎 (2房)
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 322呎 (1房)
+$728万
+$22,593/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 306呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>C | 322呎 (1房)
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 306呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
-        <is>
-          <t>D | 306呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>E | 306呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>F | 412呎 (2房)
 $916万
@@ -31368,52 +30833,52 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>B | 447呎 (2房)
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 322呎 (1房)
+$725万
+$22,528/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 306呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>C | 322呎 (1房)
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 306呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E20" s="20" t="inlineStr">
-        <is>
-          <t>D | 306呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="20" t="inlineStr">
-        <is>
-          <t>E | 306呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G20" s="20" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>F | 412呎 (2房)
--
--
-(待售)</t>
+$914万
+$22,180/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -31423,52 +30888,52 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>B | 447呎 (2房)
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 322呎 (1房)
+$725万
+$22,528/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 306呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>C | 322呎 (1房)
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 306呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
-        <is>
-          <t>D | 306呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>E | 306呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G21" s="20" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>F | 412呎 (2房)
--
--
-(待售)</t>
+$914万
+$22,180/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -31478,52 +30943,52 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 628呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>B | 447呎 (2房)
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 322呎 (1房)
+$714万
+$22,168/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 306呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
-        <is>
-          <t>C | 322呎 (1房)
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 306呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
-        <is>
-          <t>D | 306呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="20" t="inlineStr">
-        <is>
-          <t>E | 306呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>F | 412呎 (2房)
--
--
-(待售)</t>
+$908万
+$22,046/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -31549,7 +31014,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $709万
@@ -31604,7 +31069,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $707万
@@ -31659,7 +31124,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $705万
@@ -31714,7 +31179,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $703万
@@ -31769,7 +31234,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $701万
@@ -31824,7 +31289,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $699万
@@ -31879,7 +31344,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $699万
@@ -31934,7 +31399,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $695万
@@ -31989,7 +31454,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D31" s="21" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $693万
@@ -32044,7 +31509,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $691万
@@ -32068,7 +31533,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G32" s="21" t="inlineStr">
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>F | 413呎 (2房)
 $885万
@@ -32099,7 +31564,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D33" s="21" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $689万
@@ -32123,7 +31588,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G33" s="21" t="inlineStr">
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>F | 413呎 (2房)
 $884万
@@ -32154,7 +31619,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D34" s="21" t="inlineStr">
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $687万
@@ -32178,7 +31643,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G34" s="21" t="inlineStr">
+      <c r="G34" s="22" t="inlineStr">
         <is>
           <t>F | 413呎 (2房)
 $882万
@@ -32209,7 +31674,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D35" s="21" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $685万
@@ -32233,12 +31698,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G35" s="20" t="inlineStr">
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>F | 413呎 (2房)
--
--
-(待售)</t>
+$880万
+$21,308/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -32264,7 +31729,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $683万
@@ -32288,12 +31753,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G36" s="20" t="inlineStr">
+      <c r="G36" s="22" t="inlineStr">
         <is>
           <t>F | 413呎 (2房)
--
--
-(待售)</t>
+$878万
+$21,266/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -32319,7 +31784,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D37" s="21" t="inlineStr">
+      <c r="D37" s="22" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $683万
@@ -32343,12 +31808,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G37" s="20" t="inlineStr">
+      <c r="G37" s="22" t="inlineStr">
         <is>
           <t>F | 413呎 (2房)
--
--
-(待售)</t>
+$878万
+$21,266/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -32374,7 +31839,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D38" s="21" t="inlineStr">
+      <c r="D38" s="22" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $679万
@@ -32382,7 +31847,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E38" s="21" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $661万
@@ -32398,7 +31863,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G38" s="21" t="inlineStr">
+      <c r="G38" s="22" t="inlineStr">
         <is>
           <t>F | 413呎 (2房)
 $875万
@@ -32429,7 +31894,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D39" s="21" t="inlineStr">
+      <c r="D39" s="22" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $672万
@@ -32437,7 +31902,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E39" s="21" t="inlineStr">
+      <c r="E39" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $654万
@@ -32453,7 +31918,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G39" s="21" t="inlineStr">
+      <c r="G39" s="22" t="inlineStr">
         <is>
           <t>F | 413呎 (2房)
 $862万
@@ -32484,7 +31949,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D40" s="21" t="inlineStr">
+      <c r="D40" s="22" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $664万
@@ -32492,7 +31957,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E40" s="21" t="inlineStr">
+      <c r="E40" s="22" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $646万
@@ -32508,7 +31973,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G40" s="21" t="inlineStr">
+      <c r="G40" s="22" t="inlineStr">
         <is>
           <t>F | 413呎 (2房)
 $832万
@@ -32523,52 +31988,52 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B41" s="20" t="inlineStr">
+      <c r="B41" s="21" t="inlineStr">
         <is>
           <t>A | 588呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>B | 409呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C41" s="20" t="inlineStr">
-        <is>
-          <t>B | 409呎 (2房)
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>D | 270呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D41" s="20" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>E | 269呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E41" s="20" t="inlineStr">
-        <is>
-          <t>D | 270呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F41" s="20" t="inlineStr">
-        <is>
-          <t>E | 269呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G41" s="20" t="inlineStr">
+      <c r="G41" s="21" t="inlineStr">
         <is>
           <t>F | 375呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-西南九龙-叡璟II.xlsx
+++ b/files/九龙-西南九龙-叡璟II.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,11 +126,6 @@
       <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -202,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -265,9 +260,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1109,7 +1101,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1451,7 +1443,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1793,7 +1785,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2135,7 +2127,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2477,7 +2469,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -2819,7 +2811,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -3161,7 +3153,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -3223,7 +3215,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -3495,7 +3487,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -3557,7 +3549,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -3829,7 +3821,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -3891,7 +3883,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -4163,7 +4155,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -4225,7 +4217,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -4497,7 +4489,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -4559,7 +4551,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -4831,7 +4823,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -4893,7 +4885,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -5165,7 +5157,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -5227,7 +5219,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -5499,7 +5491,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -5561,7 +5553,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -5833,7 +5825,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -5895,7 +5887,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -6167,7 +6159,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -6229,7 +6221,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -6501,7 +6493,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -6563,7 +6555,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
@@ -6835,7 +6827,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -6897,7 +6889,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -7029,7 +7021,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -7091,7 +7083,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -7153,7 +7145,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
@@ -7215,7 +7207,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -7347,7 +7339,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -7409,7 +7401,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -7471,7 +7463,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -7533,7 +7525,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -7665,7 +7657,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -7727,7 +7719,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -7789,7 +7781,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -7851,7 +7843,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
@@ -7983,7 +7975,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -8045,7 +8037,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -8107,7 +8099,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -8169,7 +8161,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -8301,7 +8293,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
@@ -8363,7 +8355,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
@@ -8425,7 +8417,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -8487,7 +8479,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -8619,7 +8611,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
@@ -8681,7 +8673,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -8743,7 +8735,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
@@ -8805,7 +8797,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -8937,7 +8929,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -8999,7 +8991,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -9061,7 +9053,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -9123,7 +9115,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
@@ -9255,7 +9247,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -9317,7 +9309,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
@@ -9379,7 +9371,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
@@ -9441,7 +9433,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
@@ -9573,7 +9565,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -9635,7 +9627,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
@@ -9697,7 +9689,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -9759,7 +9751,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -9891,7 +9883,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -9953,7 +9945,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -10015,7 +10007,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
@@ -10077,7 +10069,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -10209,7 +10201,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -10271,7 +10263,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
@@ -10333,7 +10325,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
@@ -10395,7 +10387,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
@@ -10527,7 +10519,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
@@ -10589,7 +10581,7 @@
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
@@ -10651,7 +10643,7 @@
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
@@ -10713,7 +10705,7 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
@@ -10845,7 +10837,7 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
@@ -10907,7 +10899,7 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
@@ -10969,7 +10961,7 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
@@ -11031,7 +11023,7 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -11163,7 +11155,7 @@
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
@@ -11225,7 +11217,7 @@
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
@@ -11287,7 +11279,7 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
@@ -11349,7 +11341,7 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -11481,7 +11473,7 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
@@ -11543,7 +11535,7 @@
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
@@ -11605,7 +11597,7 @@
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
@@ -11667,7 +11659,7 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -11799,7 +11791,7 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
@@ -11861,7 +11853,7 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -11923,7 +11915,7 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -11985,7 +11977,7 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -12117,7 +12109,7 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
@@ -12179,7 +12171,7 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -12241,7 +12233,7 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -12303,7 +12295,7 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
@@ -12435,7 +12427,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -12497,7 +12489,7 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
@@ -14799,7 +14791,7 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -15211,7 +15203,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -15623,7 +15615,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -16035,7 +16027,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -16447,7 +16439,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -16649,7 +16641,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -16851,7 +16843,7 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -17053,7 +17045,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -17255,7 +17247,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -17457,7 +17449,7 @@
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -17659,7 +17651,7 @@
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -17861,7 +17853,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -18063,7 +18055,7 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -18265,7 +18257,7 @@
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -18467,7 +18459,7 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -18669,7 +18661,7 @@
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -18871,7 +18863,7 @@
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -19073,7 +19065,7 @@
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -19275,7 +19267,7 @@
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -19477,7 +19469,7 @@
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -19679,7 +19671,7 @@
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -19881,7 +19873,7 @@
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -20083,7 +20075,7 @@
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
@@ -20495,7 +20487,7 @@
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
@@ -20907,7 +20899,7 @@
       </c>
       <c r="F305" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G305" s="3" t="inlineStr">
@@ -21319,7 +21311,7 @@
       </c>
       <c r="F311" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G311" s="3" t="inlineStr">
@@ -21731,7 +21723,7 @@
       </c>
       <c r="F317" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
@@ -22143,7 +22135,7 @@
       </c>
       <c r="F323" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G323" s="3" t="inlineStr">
@@ -22555,7 +22547,7 @@
       </c>
       <c r="F329" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G329" s="3" t="inlineStr">
@@ -22967,7 +22959,7 @@
       </c>
       <c r="F335" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G335" s="3" t="inlineStr">
@@ -23379,7 +23371,7 @@
       </c>
       <c r="F341" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G341" s="3" t="inlineStr">
@@ -23791,7 +23783,7 @@
       </c>
       <c r="F347" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G347" s="3" t="inlineStr">
@@ -23993,7 +23985,7 @@
       </c>
       <c r="F350" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G350" s="3" t="inlineStr">
@@ -24195,7 +24187,7 @@
       </c>
       <c r="F353" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G353" s="3" t="inlineStr">
@@ -24397,7 +24389,7 @@
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
@@ -24599,7 +24591,7 @@
       </c>
       <c r="F359" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G359" s="3" t="inlineStr">
@@ -24801,7 +24793,7 @@
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
@@ -25003,7 +24995,7 @@
       </c>
       <c r="F365" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G365" s="3" t="inlineStr">
@@ -25205,7 +25197,7 @@
       </c>
       <c r="F368" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G368" s="3" t="inlineStr">
@@ -25407,7 +25399,7 @@
       </c>
       <c r="F371" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G371" s="3" t="inlineStr">
@@ -25609,7 +25601,7 @@
       </c>
       <c r="F374" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G374" s="3" t="inlineStr">
@@ -25811,7 +25803,7 @@
       </c>
       <c r="F377" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G377" s="3" t="inlineStr">
@@ -26013,7 +26005,7 @@
       </c>
       <c r="F380" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G380" s="3" t="inlineStr">
@@ -26215,7 +26207,7 @@
       </c>
       <c r="F383" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G383" s="3" t="inlineStr">
@@ -26417,7 +26409,7 @@
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G386" s="3" t="inlineStr">
@@ -26549,7 +26541,7 @@
       </c>
       <c r="F388" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G388" s="3" t="inlineStr">
@@ -26611,7 +26603,7 @@
       </c>
       <c r="F389" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G389" s="3" t="inlineStr">
@@ -26813,7 +26805,7 @@
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G392" s="3" t="inlineStr">
@@ -26945,7 +26937,7 @@
       </c>
       <c r="F394" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G394" s="3" t="inlineStr">
@@ -27007,7 +26999,7 @@
       </c>
       <c r="F395" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G395" s="3" t="inlineStr">
@@ -27209,7 +27201,7 @@
       </c>
       <c r="F398" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G398" s="3" t="inlineStr">
@@ -27341,7 +27333,7 @@
       </c>
       <c r="F400" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G400" s="3" t="inlineStr">
@@ -27403,7 +27395,7 @@
       </c>
       <c r="F401" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G401" s="3" t="inlineStr">
@@ -28072,12 +28064,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>121</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -28213,12 +28205,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1188万
 $25,889/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -28260,12 +28252,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1170万
 $25,481/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -28307,12 +28299,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1138万
 $24,786/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -28354,12 +28346,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1126万
 $24,542/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -28401,12 +28393,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1115万
 $24,298/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -28448,12 +28440,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1104万
 $24,059/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -28487,20 +28479,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1115万
 $24,193/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F12" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1093万
 $23,821/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -28534,20 +28526,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1102万
 $23,907/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1080万
 $23,538/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -28581,20 +28573,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1098万
 $23,811/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1076万
 $23,444/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -28628,20 +28620,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1093万
 $23,716/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1072万
 $23,351/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -28675,20 +28667,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1089万
 $23,620/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1068万
 $23,257/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -28722,20 +28714,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1085万
 $23,527/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1063万
 $23,166/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -28769,20 +28761,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1080万
 $23,434/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1059万
 $23,072/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -28816,20 +28808,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1076万
 $23,341/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F19" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1055万
 $22,980/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -28863,20 +28855,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1072万
 $23,247/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F20" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1051万
 $22,889/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -28910,20 +28902,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1072万
 $23,247/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F21" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1051万
 $22,889/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -28957,20 +28949,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1063万
 $23,063/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
 $1042万
 $22,708/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -28980,20 +28972,20 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1773万
 $24,526/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1787万
 $24,474/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -29004,20 +28996,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1041万
 $22,590/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $1034万
 $22,480/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29027,20 +29019,20 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1752万
 $24,235/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1765万
 $24,184/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -29051,20 +29043,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1038万
 $22,523/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $1031万
 $22,413/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29074,20 +29066,20 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1731万
 $23,947/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1744万
 $23,897/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -29098,20 +29090,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1035万
 $22,456/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F25" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $1028万
 $22,346/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29121,20 +29113,20 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1711万
 $23,664/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C26" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1724万
 $23,614/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -29145,20 +29137,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1032万
 $22,388/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F26" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $1025万
 $22,278/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29168,20 +29160,20 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1691万
 $23,383/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1703万
 $23,334/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -29192,20 +29184,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1029万
 $22,321/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F27" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $1022万
 $22,213/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29215,20 +29207,20 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1671万
 $23,107/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1683万
 $23,058/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -29239,20 +29231,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1026万
 $22,254/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F28" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $1019万
 $22,146/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29262,20 +29254,20 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1671万
 $23,107/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1683万
 $23,058/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -29286,20 +29278,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1026万
 $22,254/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F29" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $1019万
 $22,146/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29309,20 +29301,20 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1657万
 $22,921/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C30" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1670万
 $22,873/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -29333,20 +29325,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1020万
 $22,119/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F30" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $1013万
 $22,013/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29356,20 +29348,20 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1651万
 $22,830/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1663万
 $22,781/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -29380,20 +29372,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1017万
 $22,054/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F31" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $1010万
 $21,946/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29403,20 +29395,20 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1644万
 $22,739/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C32" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1656万
 $22,690/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -29427,20 +29419,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1014万
 $21,987/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F32" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $1006万
 $21,880/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29450,20 +29442,20 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1637万
 $22,647/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C33" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1650万
 $22,600/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -29474,20 +29466,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1011万
 $21,922/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F33" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $1004万
 $21,815/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29497,20 +29489,20 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1631万
 $22,557/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C34" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1643万
 $22,510/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -29521,20 +29513,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1008万
 $21,857/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F34" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $1000万
 $21,750/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29544,20 +29536,20 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1624万
 $22,466/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C35" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1637万
 $22,419/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -29568,20 +29560,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E35" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1004万
 $21,790/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F35" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $998万
 $21,685/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29591,20 +29583,20 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1618万
 $22,376/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C36" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1630万
 $22,329/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -29615,20 +29607,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
+      <c r="E36" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1002万
 $21,725/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F36" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $994万
 $21,620/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29638,20 +29630,20 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B37" s="22" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1618万
 $22,376/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C37" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1630万
 $22,329/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -29662,20 +29654,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="E37" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $1002万
 $21,725/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F37" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $994万
 $21,620/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29685,20 +29677,20 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B38" s="22" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1605万
 $22,198/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C38" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1617万
 $22,151/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
@@ -29709,20 +29701,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E38" s="22" t="inlineStr">
+      <c r="E38" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $996万
 $21,594/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F38" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $988万
 $21,489/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29732,20 +29724,20 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B39" s="22" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1598万
 $22,109/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C39" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1610万
 $22,062/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -29756,20 +29748,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E39" s="22" t="inlineStr">
+      <c r="E39" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $992万
 $21,529/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F39" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $986万
 $21,426/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29779,20 +29771,20 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B40" s="22" t="inlineStr">
+      <c r="B40" s="21" t="inlineStr">
         <is>
           <t>A | 723呎 (3房)
 $1592万
 $22,021/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C40" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 $1604万
 $21,974/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
@@ -29803,20 +29795,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E40" s="22" t="inlineStr">
+      <c r="E40" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
 $987万
 $21,401/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F40" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F40" s="21" t="inlineStr">
         <is>
           <t>E | 460呎 (2房)
 $980万
 $21,296/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29941,12 +29933,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>67</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -30244,12 +30236,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 322呎 (1房)
 $760万
 $23,609/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -30299,12 +30291,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 322呎 (1房)
 $753万
 $23,373/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -30354,12 +30346,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 322呎 (1房)
 $745万
 $23,143/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -30409,12 +30401,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 322呎 (1房)
 $745万
 $23,143/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -30464,12 +30456,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 322呎 (1房)
 $741万
 $23,003/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -30519,12 +30511,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 322呎 (1房)
 $738万
 $22,935/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -30543,12 +30535,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>F | 412呎 (2房)
 $950万
 $23,058/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -30574,12 +30566,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 322呎 (1房)
 $736万
 $22,866/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -30598,12 +30590,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>F | 412呎 (2房)
 $941万
 $22,830/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -30629,12 +30621,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 322呎 (1房)
 $734万
 $22,798/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -30653,12 +30645,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 412呎 (2房)
 $931万
 $22,602/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -30684,12 +30676,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 322呎 (1房)
 $732万
 $22,730/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -30708,12 +30700,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>F | 412呎 (2房)
 $922万
 $22,379/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -30739,12 +30731,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 322呎 (1房)
 $730万
 $22,661/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -30763,12 +30755,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>F | 412呎 (2房)
 $919万
 $22,313/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -30794,12 +30786,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 322呎 (1房)
 $728万
 $22,593/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -30818,12 +30810,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 412呎 (2房)
 $916万
 $22,245/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -30849,12 +30841,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 322呎 (1房)
 $725万
 $22,528/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -30873,12 +30865,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G20" s="22" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 412呎 (2房)
 $914万
 $22,180/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -30904,12 +30896,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 322呎 (1房)
 $725万
 $22,528/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -30928,12 +30920,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 412呎 (2房)
 $914万
 $22,180/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -30959,12 +30951,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 322呎 (1房)
 $714万
 $22,168/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -30983,12 +30975,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G22" s="22" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 412呎 (2房)
 $908万
 $22,046/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -31014,12 +31006,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $709万
 $21,954/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -31069,12 +31061,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $707万
 $21,889/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -31124,12 +31116,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $705万
 $21,827/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -31179,12 +31171,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $703万
 $21,765/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -31234,12 +31226,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $701万
 $21,700/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -31289,12 +31281,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $699万
 $21,638/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -31344,12 +31336,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $699万
 $21,638/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -31399,12 +31391,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $695万
 $21,514/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -31454,12 +31446,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $693万
 $21,452/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -31509,12 +31501,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="21" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $691万
 $21,390/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -31533,12 +31525,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G32" s="22" t="inlineStr">
+      <c r="G32" s="21" t="inlineStr">
         <is>
           <t>F | 413呎 (2房)
 $885万
 $21,436/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -31564,12 +31556,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D33" s="21" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $689万
 $21,328/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -31588,12 +31580,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G33" s="22" t="inlineStr">
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>F | 413呎 (2房)
 $884万
 $21,395/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -31619,12 +31611,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="21" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $687万
 $21,266/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -31643,12 +31635,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G34" s="22" t="inlineStr">
+      <c r="G34" s="21" t="inlineStr">
         <is>
           <t>F | 413呎 (2房)
 $882万
 $21,351/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -31674,12 +31666,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="21" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $685万
 $21,204/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -31698,12 +31690,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G35" s="22" t="inlineStr">
+      <c r="G35" s="21" t="inlineStr">
         <is>
           <t>F | 413呎 (2房)
 $880万
 $21,308/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -31729,12 +31721,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D36" s="22" t="inlineStr">
+      <c r="D36" s="21" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $683万
 $21,146/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
@@ -31753,12 +31745,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G36" s="22" t="inlineStr">
+      <c r="G36" s="21" t="inlineStr">
         <is>
           <t>F | 413呎 (2房)
 $878万
 $21,266/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -31784,12 +31776,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D37" s="22" t="inlineStr">
+      <c r="D37" s="21" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $683万
 $21,146/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
@@ -31808,12 +31800,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G37" s="22" t="inlineStr">
+      <c r="G37" s="21" t="inlineStr">
         <is>
           <t>F | 413呎 (2房)
 $878万
 $21,266/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -31839,20 +31831,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D38" s="22" t="inlineStr">
+      <c r="D38" s="21" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $679万
 $21,022/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E38" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $661万
 $21,521/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
@@ -31863,12 +31855,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G38" s="22" t="inlineStr">
+      <c r="G38" s="21" t="inlineStr">
         <is>
           <t>F | 413呎 (2房)
 $875万
 $21,182/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -31894,20 +31886,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D39" s="22" t="inlineStr">
+      <c r="D39" s="21" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $672万
 $20,811/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E39" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $654万
 $21,306/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
@@ -31918,12 +31910,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G39" s="22" t="inlineStr">
+      <c r="G39" s="21" t="inlineStr">
         <is>
           <t>F | 413呎 (2房)
 $862万
 $20,862/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -31949,20 +31941,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D40" s="22" t="inlineStr">
+      <c r="D40" s="21" t="inlineStr">
         <is>
           <t>C | 323呎 (1房)
 $664万
 $20,551/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E40" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E40" s="21" t="inlineStr">
         <is>
           <t>D | 307呎 (1房)
 $646万
 $21,039/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
@@ -31973,12 +31965,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G40" s="22" t="inlineStr">
+      <c r="G40" s="21" t="inlineStr">
         <is>
           <t>F | 413呎 (2房)
 $832万
 $20,153/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-西南九龙-叡璟II.xlsx
+++ b/files/九龙-西南九龙-叡璟II.xlsx
@@ -3879,38 +3879,30 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>17227000</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>23599</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L51" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K51" s="5" t="n">
+        <v>17227000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>23599</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -3919,7 +3911,7 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4817,38 +4809,30 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>16720000</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>22904</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L66" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K66" s="5" t="n">
+        <v>16720000</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>22904</v>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
@@ -4857,7 +4841,7 @@
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5135,38 +5119,30 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>16555000</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>22678</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K71" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L71" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K71" s="5" t="n">
+        <v>16555000</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>22678</v>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
@@ -5175,7 +5151,7 @@
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6383,38 +6359,30 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I91" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>16300000</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>22329</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K91" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L91" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K91" s="5" t="n">
+        <v>16300000</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>22329</v>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
@@ -6423,7 +6391,7 @@
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -12561,38 +12529,30 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H190" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I190" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H190" s="5" t="n">
+        <v>7512000</v>
+      </c>
+      <c r="I190" s="5" t="n">
+        <v>24549</v>
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K190" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L190" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K190" s="5" t="n">
+        <v>7512000</v>
+      </c>
+      <c r="L190" s="5" t="n">
+        <v>24549</v>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
@@ -12601,7 +12561,7 @@
       </c>
       <c r="N190" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -17023,38 +16983,30 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H259" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I259" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H259" s="5" t="n">
+        <v>14229000</v>
+      </c>
+      <c r="I259" s="5" t="n">
+        <v>22658</v>
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K259" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L259" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K259" s="5" t="n">
+        <v>14229000</v>
+      </c>
+      <c r="L259" s="5" t="n">
+        <v>22658</v>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
@@ -17063,7 +17015,7 @@
       </c>
       <c r="N259" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -17411,38 +17363,30 @@
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H265" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I265" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H265" s="5" t="n">
+        <v>14088000</v>
+      </c>
+      <c r="I265" s="5" t="n">
+        <v>22433</v>
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K265" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L265" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K265" s="5" t="n">
+        <v>14088000</v>
+      </c>
+      <c r="L265" s="5" t="n">
+        <v>22433</v>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
@@ -17451,7 +17395,7 @@
       </c>
       <c r="N265" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -26672,7 +26616,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26682,7 +26626,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>165</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27165,12 +27109,12 @@
 (26年-10月-03日)</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
-招标单位
--
-(在售)</t>
+$1723万
+$23,599/呎
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -27306,12 +27250,12 @@
 (26年-10月-03日)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
-招标单位
--
-(在售)</t>
+$1672万
+$22,904/呎
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -27353,12 +27297,12 @@
 (26年-10月-03日)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
-招标单位
--
-(在售)</t>
+$1656万
+$22,678/呎
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -27541,12 +27485,12 @@
 (26年-10月-03日)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
-招标单位
--
-(在售)</t>
+$1630万
+$22,329/呎
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -28541,7 +28485,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -28551,7 +28495,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>170</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -28632,12 +28576,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>D | 306呎 (1房)
-招标单位
--
-(在售)</t>
+$751万
+$24,549/呎
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -29213,12 +29157,12 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 628呎 (3房)
-招标单位
--
-(在售)</t>
+$1423万
+$22,658/呎
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -29268,12 +29212,12 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 628呎 (3房)
-招标单位
--
-(在售)</t>
+$1409万
+$22,433/呎
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">

--- a/files/九龙-西南九龙-叡璟II.xlsx
+++ b/files/九龙-西南九龙-叡璟II.xlsx
@@ -1365,38 +1365,30 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>19226000</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>26629</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K12" s="5" t="n">
+        <v>19226000</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>26629</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1405,7 +1397,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3561,38 +3553,30 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>17399000</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>23834</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K46" s="5" t="n">
+        <v>17399000</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>23834</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
@@ -3601,7 +3585,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -26616,7 +26600,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26626,7 +26610,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>167</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -26725,7 +26709,54 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 722呎 (3房)
+$1923万
+$26,629/呎
+(26年-10月-11日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 730呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 713呎 (3房)
+$1848万
+$25,913/呎
+(26年-09月-27日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 461呎 (2房)
+$1110万
+$24,072/呎
+(26年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 459呎 (2房)
+$1022万
+$22,266/呎
+(26年-09月-27日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 722呎 (3房)
 招标单位
@@ -26733,7 +26764,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 招标单位
@@ -26741,38 +26772,38 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
-$1848万
-$25,913/呎
+$1811万
+$25,405/呎
 (26年-09月-27日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
-$1110万
-$24,072/呎
+$1092万
+$23,694/呎
 (26年-10月-03日)</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
-$1022万
-$22,266/呎
+$1076万
+$23,444/呎
 (26年-09月-27日)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 722呎 (3房)
 招标单位
@@ -26780,7 +26811,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 招标单位
@@ -26788,38 +26819,38 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
-$1811万
-$25,405/呎
+$1742万
+$24,428/呎
 (26年-09月-27日)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
-$1092万
-$23,694/呎
+$970万
+$21,043/呎
 (26年-10月-03日)</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
-$1076万
-$23,444/呎
+$956万
+$20,821/呎
 (26年-09月-27日)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 722呎 (3房)
 招标单位
@@ -26827,7 +26858,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 招标单位
@@ -26835,38 +26866,38 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
-$1742万
-$24,428/呎
+$1724万
+$24,185/呎
 (26年-09月-27日)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
-$970万
-$21,043/呎
+$983万
+$21,332/呎
 (26年-10月-03日)</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
-$956万
-$20,821/呎
+$969万
+$21,107/呎
 (26年-09月-27日)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 722呎 (3房)
 招标单位
@@ -26874,7 +26905,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 招标单位
@@ -26882,46 +26913,46 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
-$1724万
-$24,185/呎
+$1707万
+$23,947/呎
 (26年-09月-27日)</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
-$983万
-$21,332/呎
+$951万
+$20,629/呎
 (26年-10月-03日)</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
-$969万
-$21,107/呎
+$937万
+$20,412/呎
 (26年-09月-27日)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 722呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
+$1759万
+$24,364/呎
+(26年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 招标单位
@@ -26929,46 +26960,46 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
-$1707万
-$23,947/呎
+$1690万
+$23,710/呎
 (26年-09月-27日)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
-$951万
-$20,629/呎
+$942万
+$20,425/呎
 (26年-10月-03日)</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
-$937万
-$20,412/呎
+$928万
+$20,211/呎
 (26年-09月-27日)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 722呎 (3房)
-$1759万
-$24,364/呎
+$1743万
+$24,141/呎
 (26年-10月-03日)</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 招标单位
@@ -26976,53 +27007,6 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>C | 713呎 (3房)
-$1690万
-$23,710/呎
-(26年-09月-27日)</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="inlineStr">
-        <is>
-          <t>D | 461呎 (2房)
-$942万
-$20,425/呎
-(26年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>E | 459呎 (2房)
-$928万
-$20,211/呎
-(26年-09月-27日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>A | 722呎 (3房)
-$1743万
-$24,141/呎
-(26年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>B | 730呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
@@ -27062,12 +27046,12 @@
 (26年-10月-03日)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
-招标单位
--
-(在售)</t>
+$1740万
+$23,834/呎
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">

--- a/files/九龙-西南九龙-叡璟II.xlsx
+++ b/files/九龙-西南九龙-叡璟II.xlsx
@@ -14924,7 +14924,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -17034,7 +17034,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -17228,7 +17228,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -21788,7 +21788,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -24068,7 +24068,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -28887,7 +28887,7 @@
           <t>C | 322呎 (1房)
 $686万
 $21,292/呎
-(26年-09月-27日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -29217,7 +29217,7 @@
           <t>C | 322呎 (1房)
 $615万
 $19,093/呎
-(26年-09月-27日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -29241,7 +29241,7 @@
           <t>F | 412呎 (2房)
 $774万
 $18,799/呎
-(26年-09月-27日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -29547,7 +29547,7 @@
           <t>C | 323呎 (1房)
 $652万
 $20,198/呎
-(26年-09月-27日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -29877,7 +29877,7 @@
           <t>C | 323呎 (1房)
 $643万
 $19,907/呎
-(26年-09月-27日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -30207,7 +30207,7 @@
           <t>C | 323呎 (1房)
 $575万
 $17,814/呎
-(26年-09月-27日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">

--- a/files/九龙-西南九龙-叡璟II.xlsx
+++ b/files/九龙-西南九龙-叡璟II.xlsx
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1683,38 +1683,30 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>18849000</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>26107</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K17" s="5" t="n">
+        <v>18849000</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>26107</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -1723,7 +1715,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1750,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1882,7 +1874,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2084,7 +2076,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2146,7 +2138,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2208,7 +2200,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2410,7 +2402,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2472,7 +2464,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2534,7 +2526,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2736,7 +2728,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2798,7 +2790,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2860,7 +2852,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2992,7 +2984,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3054,7 +3046,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3116,7 +3108,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3178,7 +3170,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3310,7 +3302,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3372,7 +3364,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3434,7 +3426,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3496,7 +3488,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3682,7 +3674,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3744,7 +3736,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3806,7 +3798,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3930,7 +3922,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3992,7 +3984,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4054,7 +4046,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4116,7 +4108,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4178,7 +4170,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4240,7 +4232,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4302,7 +4294,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4364,7 +4356,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4426,7 +4418,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4488,7 +4480,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4550,7 +4542,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4612,7 +4604,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4674,7 +4666,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4736,7 +4728,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4860,7 +4852,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4922,7 +4914,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4984,7 +4976,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5046,7 +5038,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5108,7 +5100,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5170,7 +5162,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5232,7 +5224,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5294,7 +5286,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5356,7 +5348,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5418,7 +5410,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5480,7 +5472,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5542,7 +5534,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5604,7 +5596,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5666,7 +5658,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5728,7 +5720,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5790,7 +5782,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5852,7 +5844,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5914,7 +5906,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5976,7 +5968,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6038,7 +6030,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6100,7 +6092,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6162,7 +6154,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6224,7 +6216,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6286,7 +6278,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6410,7 +6402,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6472,7 +6464,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6534,7 +6526,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6596,7 +6588,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6658,7 +6650,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6720,7 +6712,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6782,7 +6774,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6844,7 +6836,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6906,7 +6898,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6968,7 +6960,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7030,7 +7022,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7092,7 +7084,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7154,7 +7146,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7216,7 +7208,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7278,7 +7270,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7340,7 +7332,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7402,7 +7394,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7464,7 +7456,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7526,7 +7518,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7588,7 +7580,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7650,7 +7642,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7712,7 +7704,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7774,7 +7766,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7836,7 +7828,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7898,7 +7890,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7960,7 +7952,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8022,7 +8014,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8084,7 +8076,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8146,7 +8138,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8208,7 +8200,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8270,7 +8262,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8332,7 +8324,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8394,7 +8386,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8456,7 +8448,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8518,7 +8510,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8580,7 +8572,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8642,7 +8634,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8704,7 +8696,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8766,7 +8758,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8828,7 +8820,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8890,7 +8882,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8952,7 +8944,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9014,7 +9006,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9076,7 +9068,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9138,7 +9130,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9200,7 +9192,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9262,7 +9254,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9324,7 +9316,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9386,7 +9378,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9448,7 +9440,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9510,7 +9502,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9572,7 +9564,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9634,7 +9626,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9696,7 +9688,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9758,7 +9750,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9820,7 +9812,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9882,7 +9874,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9944,7 +9936,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -10006,7 +9998,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10068,7 +10060,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10130,7 +10122,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10192,7 +10184,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10254,7 +10246,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10316,7 +10308,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10378,7 +10370,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10440,7 +10432,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10502,7 +10494,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10564,7 +10556,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10626,7 +10618,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10688,7 +10680,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10750,7 +10742,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10812,7 +10804,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10874,7 +10866,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10936,7 +10928,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10998,7 +10990,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11060,7 +11052,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11122,7 +11114,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11184,7 +11176,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11246,7 +11238,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11308,7 +11300,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11370,7 +11362,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11432,7 +11424,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11494,7 +11486,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11556,7 +11548,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11618,7 +11610,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11680,7 +11672,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11742,7 +11734,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11804,7 +11796,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11866,7 +11858,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11928,7 +11920,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11990,7 +11982,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12052,7 +12044,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12114,7 +12106,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12176,7 +12168,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12233,38 +12225,30 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H186" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I186" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="H186" s="5" t="n">
+        <v>18334000</v>
+      </c>
+      <c r="I186" s="5" t="n">
+        <v>26726</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K186" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L186" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K186" s="5" t="n">
+        <v>18334000</v>
+      </c>
+      <c r="L186" s="5" t="n">
+        <v>26726</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
@@ -12273,7 +12257,7 @@
       </c>
       <c r="N186" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -12575,38 +12559,30 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H191" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I191" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H191" s="5" t="n">
+        <v>8010000</v>
+      </c>
+      <c r="I191" s="5" t="n">
+        <v>24876</v>
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K191" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L191" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K191" s="5" t="n">
+        <v>8010000</v>
+      </c>
+      <c r="L191" s="5" t="n">
+        <v>24876</v>
       </c>
       <c r="M191" s="3" t="inlineStr">
         <is>
@@ -12615,7 +12591,7 @@
       </c>
       <c r="N191" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -14148,7 +14124,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14342,7 +14318,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14474,7 +14450,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14536,7 +14512,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14598,7 +14574,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -15312,7 +15288,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15374,7 +15350,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15700,7 +15676,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15894,7 +15870,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -16026,7 +16002,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -16088,7 +16064,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -16150,7 +16126,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -16212,7 +16188,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -16274,7 +16250,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16406,7 +16382,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16468,7 +16444,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16530,7 +16506,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16592,7 +16568,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16654,7 +16630,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16786,7 +16762,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16848,7 +16824,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16910,7 +16886,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -17166,7 +17142,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -17290,7 +17266,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17414,7 +17390,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17608,7 +17584,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17732,7 +17708,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17794,7 +17770,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17926,7 +17902,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17988,7 +17964,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -18050,7 +18026,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -18112,7 +18088,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -18174,7 +18150,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -18306,7 +18282,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18368,7 +18344,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18430,7 +18406,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18492,7 +18468,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18554,7 +18530,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18686,7 +18662,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18748,7 +18724,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18810,7 +18786,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18872,7 +18848,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18934,7 +18910,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -19066,7 +19042,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -19128,7 +19104,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -19190,7 +19166,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -19252,7 +19228,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -19314,7 +19290,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19446,7 +19422,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19570,7 +19546,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19632,7 +19608,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19694,7 +19670,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19826,7 +19802,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -19888,7 +19864,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -19950,7 +19926,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -20012,7 +19988,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -20074,7 +20050,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -20206,7 +20182,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -20268,7 +20244,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -20392,7 +20368,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20454,7 +20430,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20586,7 +20562,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -20648,7 +20624,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -20710,7 +20686,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -20834,7 +20810,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -20966,7 +20942,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -21028,7 +21004,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -21090,7 +21066,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -21152,7 +21128,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -21214,7 +21190,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -21346,7 +21322,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -21408,7 +21384,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21470,7 +21446,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21532,7 +21508,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -21594,7 +21570,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21726,7 +21702,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21850,7 +21826,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -21912,7 +21888,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -21974,7 +21950,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -22106,7 +22082,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -22168,7 +22144,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -22230,7 +22206,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -22292,7 +22268,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -22354,7 +22330,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -22486,7 +22462,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22548,7 +22524,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -22610,7 +22586,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -22672,7 +22648,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -22734,7 +22710,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -22866,7 +22842,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -22928,7 +22904,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -22990,7 +22966,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -23052,7 +23028,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -23114,7 +23090,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -23246,7 +23222,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -23308,7 +23284,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -23370,7 +23346,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -23432,7 +23408,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23494,7 +23470,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -23626,7 +23602,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -23688,7 +23664,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -23750,7 +23726,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -23812,7 +23788,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -23874,7 +23850,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -24006,7 +23982,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -24130,7 +24106,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -24192,7 +24168,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -24254,7 +24230,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -24386,7 +24362,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -24448,7 +24424,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -24510,7 +24486,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -24572,7 +24548,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -24634,7 +24610,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -24766,7 +24742,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -24828,7 +24804,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -24890,7 +24866,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -24952,7 +24928,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -25014,7 +24990,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -25146,7 +25122,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -25208,7 +25184,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -25332,7 +25308,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -25394,7 +25370,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -25526,7 +25502,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -25588,7 +25564,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -25650,7 +25626,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -25712,7 +25688,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -25774,7 +25750,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -25906,7 +25882,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -25968,7 +25944,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -26030,7 +26006,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -26092,7 +26068,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -26154,7 +26130,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -26426,7 +26402,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -26483,38 +26459,30 @@
       </c>
       <c r="F409" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H409" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I409" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H409" s="5" t="n">
+        <v>14430000</v>
+      </c>
+      <c r="I409" s="5" t="n">
+        <v>24541</v>
       </c>
       <c r="J409" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K409" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L409" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K409" s="5" t="n">
+        <v>14430000</v>
+      </c>
+      <c r="L409" s="5" t="n">
+        <v>24541</v>
       </c>
       <c r="M409" s="3" t="inlineStr">
         <is>
@@ -26523,7 +26491,7 @@
       </c>
       <c r="N409" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -26600,7 +26568,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26610,7 +26578,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -26730,7 +26698,7 @@
           <t>C | 713呎 (3房)
 $1848万
 $25,913/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -26738,7 +26706,7 @@
           <t>D | 461呎 (2房)
 $1110万
 $24,072/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -26746,7 +26714,7 @@
           <t>E | 459呎 (2房)
 $1022万
 $22,266/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -26756,7 +26724,54 @@
           <t>43</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 722呎 (3房)
+$1885万
+$26,107/呎
+(26年-10月-23日)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 730呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 713呎 (3房)
+$1811万
+$25,405/呎
+(26年-10月-21日)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 461呎 (2房)
+$1092万
+$23,694/呎
+(26年-10月-27日)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 459呎 (2房)
+$1076万
+$23,444/呎
+(26年-10月-21日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 722呎 (3房)
 招标单位
@@ -26764,7 +26779,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 招标单位
@@ -26772,38 +26787,38 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
-$1811万
-$25,405/呎
-(26年-09月-27日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
+$1742万
+$24,428/呎
+(26年-10月-20日)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
-$1092万
-$23,694/呎
+$970万
+$21,043/呎
 (26年-10月-03日)</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
-$1076万
-$23,444/呎
-(26年-09月-27日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
+$956万
+$20,821/呎
+(26年-10月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 722呎 (3房)
 招标单位
@@ -26811,7 +26826,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 招标单位
@@ -26819,38 +26834,38 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
-$1742万
-$24,428/呎
-(26年-09月-27日)</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
+$1724万
+$24,185/呎
+(26年-10月-20日)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
-$970万
-$21,043/呎
-(26年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
+$983万
+$21,332/呎
+(26年-10月-27日)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
-$956万
-$20,821/呎
-(26年-09月-27日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
+$969万
+$21,107/呎
+(26年-10月-21日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 722呎 (3房)
 招标单位
@@ -26858,7 +26873,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 招标单位
@@ -26866,46 +26881,46 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
-$1724万
-$24,185/呎
-(26年-09月-27日)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
+$1707万
+$23,947/呎
+(26年-10月-23日)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
-$983万
-$21,332/呎
-(26年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
+$951万
+$20,629/呎
+(26年-10月-27日)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
-$969万
-$21,107/呎
-(26年-09月-27日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
+$937万
+$20,412/呎
+(26年-10月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 722呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
+$1759万
+$24,364/呎
+(26年-10月-27日)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 招标单位
@@ -26913,46 +26928,46 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
-$1707万
-$23,947/呎
-(26年-09月-27日)</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
+$1690万
+$23,710/呎
+(26年-10月-21日)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 461呎 (2房)
-$951万
-$20,629/呎
-(26年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
+$942万
+$20,425/呎
+(26年-10月-27日)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>E | 459呎 (2房)
-$937万
-$20,412/呎
-(26年-09月-27日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
+$928万
+$20,211/呎
+(26年-10月-21日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 722呎 (3房)
-$1759万
-$24,364/呎
-(26年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
+$1743万
+$24,141/呎
+(26年-10月-27日)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 730呎 (3房)
 招标单位
@@ -26960,59 +26975,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>C | 713呎 (3房)
-$1690万
-$23,710/呎
-(26年-09月-27日)</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="inlineStr">
-        <is>
-          <t>D | 461呎 (2房)
-$942万
-$20,425/呎
-(26年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>E | 459呎 (2房)
-$928万
-$20,211/呎
-(26年-09月-27日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>A | 722呎 (3房)
-$1743万
-$24,141/呎
-(26年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>B | 730呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 713呎 (3房)
 $1674万
 $23,477/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -27020,7 +26988,7 @@
           <t>D | 461呎 (2房)
 $937万
 $20,323/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -27028,7 +26996,7 @@
           <t>E | 459呎 (2房)
 $918万
 $20,011/呎
-(26年-09月-27日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
     </row>
@@ -27059,7 +27027,7 @@
           <t>C | 713呎 (3房)
 $1657万
 $23,244/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -27067,7 +27035,7 @@
           <t>D | 461呎 (2房)
 $1014万
 $21,996/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -27075,7 +27043,7 @@
           <t>E | 459呎 (2房)
 $908万
 $19,773/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -27090,7 +27058,7 @@
           <t>A | 722呎 (3房)
 $1709万
 $23,670/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -27106,7 +27074,7 @@
           <t>C | 713呎 (3房)
 $1641万
 $23,013/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -27114,7 +27082,7 @@
           <t>D | 461呎 (2房)
 $922万
 $20,002/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -27122,7 +27090,7 @@
           <t>E | 459呎 (2房)
 $904万
 $19,695/呎
-(26年-09月-27日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -27137,7 +27105,7 @@
           <t>A | 722呎 (3房)
 $1690万
 $23,414/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -27145,7 +27113,7 @@
           <t>B | 730呎 (3房)
 $1706万
 $23,366/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -27153,7 +27121,7 @@
           <t>C | 713呎 (3房)
 $1624万
 $22,784/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -27161,7 +27129,7 @@
           <t>D | 461呎 (2房)
 $918万
 $19,922/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -27169,7 +27137,7 @@
           <t>E | 459呎 (2房)
 $900万
 $19,617/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -27184,7 +27152,7 @@
           <t>A | 722呎 (3房)
 $1674万
 $23,181/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -27192,7 +27160,7 @@
           <t>B | 730呎 (3房)
 $1689万
 $23,134/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -27200,7 +27168,7 @@
           <t>C | 713呎 (3房)
 $1608万
 $22,558/呎
-(26年-09月-28日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -27208,7 +27176,7 @@
           <t>D | 461呎 (2房)
 $915万
 $19,842/呎
-(26年-09月-27日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -27216,7 +27184,7 @@
           <t>E | 459呎 (2房)
 $982万
 $21,397/呎
-(26年-09月-27日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
     </row>
@@ -27231,7 +27199,7 @@
           <t>A | 722呎 (3房)
 $1692万
 $23,435/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -27247,7 +27215,7 @@
           <t>C | 713呎 (3房)
 $1596万
 $22,384/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -27255,7 +27223,7 @@
           <t>D | 461呎 (2房)
 $954万
 $20,705/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -27263,7 +27231,7 @@
           <t>E | 459呎 (2房)
 $893万
 $19,460/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -27278,7 +27246,7 @@
           <t>A | 722呎 (3房)
 $1711万
 $23,698/呎
-(26年-10月-03日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -27286,7 +27254,7 @@
           <t>B | 730呎 (3房)
 $1656万
 $22,678/呎
-(26年-10月-06日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -27294,7 +27262,7 @@
           <t>C | 713呎 (3房)
 $1577万
 $22,118/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -27302,7 +27270,7 @@
           <t>D | 461呎 (2房)
 $929万
 $20,154/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -27310,7 +27278,7 @@
           <t>E | 459呎 (2房)
 $890万
 $19,381/呎
-(26年-09月-27日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -27325,7 +27293,7 @@
           <t>A | 722呎 (3房)
 $1624万
 $22,500/呎
-(26年-10月-03日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -27333,7 +27301,7 @@
           <t>B | 730呎 (3房)
 $1782万
 $24,407/呎
-(26年-10月-03日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -27341,7 +27309,7 @@
           <t>C | 713呎 (3房)
 $1563万
 $21,921/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -27349,7 +27317,7 @@
           <t>D | 461呎 (2房)
 $904万
 $19,607/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -27357,7 +27325,7 @@
           <t>E | 459呎 (2房)
 $970万
 $21,144/呎
-(26年-09月-27日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -27372,7 +27340,7 @@
           <t>A | 722呎 (3房)
 $1608万
 $22,277/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -27380,7 +27348,7 @@
           <t>B | 730呎 (3房)
 $1623万
 $22,232/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -27388,7 +27356,7 @@
           <t>C | 713呎 (3房)
 $1550万
 $21,739/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -27396,7 +27364,7 @@
           <t>D | 461呎 (2房)
 $900万
 $19,529/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -27404,7 +27372,7 @@
           <t>E | 459呎 (2房)
 $883万
 $19,229/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -27419,7 +27387,7 @@
           <t>A | 722呎 (3房)
 $1598万
 $22,133/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -27427,7 +27395,7 @@
           <t>B | 730呎 (3房)
 $1608万
 $22,027/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -27435,7 +27403,7 @@
           <t>C | 713呎 (3房)
 $1550万
 $21,739/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -27443,7 +27411,7 @@
           <t>D | 461呎 (2房)
 $900万
 $19,529/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -27451,7 +27419,7 @@
           <t>E | 459呎 (2房)
 $967万
 $21,059/呎
-(26年-09月-27日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
     </row>
@@ -27466,7 +27434,7 @@
           <t>A | 722呎 (3房)
 $1644万
 $22,770/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -27482,7 +27450,7 @@
           <t>C | 713呎 (3房)
 $1515万
 $21,251/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -27490,7 +27458,7 @@
           <t>D | 461呎 (2房)
 $914万
 $19,835/呎
-(26年-09月-27日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -27498,7 +27466,7 @@
           <t>E | 459呎 (2房)
 $959万
 $20,893/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -27513,7 +27481,7 @@
           <t>A | 723呎 (3房)
 $1631万
 $22,564/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -27521,7 +27489,7 @@
           <t>B | 730呎 (3房)
 $1501万
 $20,559/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -27529,7 +27497,7 @@
           <t>C | 714呎 (3房)
 $1504万
 $21,059/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -27537,7 +27505,7 @@
           <t>D | 461呎 (2房)
 $875万
 $18,976/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -27545,7 +27513,7 @@
           <t>E | 460呎 (2房)
 $869万
 $18,885/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -27560,7 +27528,7 @@
           <t>A | 723呎 (3房)
 $1472万
 $20,358/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -27568,7 +27536,7 @@
           <t>B | 730呎 (3房)
 $1624万
 $22,249/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -27576,7 +27544,7 @@
           <t>C | 714呎 (3房)
 $1640万
 $22,973/呎
-(26年-10月-03日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -27584,7 +27552,7 @@
           <t>D | 461呎 (2房)
 $955万
 $20,722/呎
-(26年-09月-27日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -27592,7 +27560,7 @@
           <t>E | 460呎 (2房)
 $866万
 $18,828/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -27607,7 +27575,7 @@
           <t>A | 723呎 (3房)
 $1593万
 $22,032/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -27615,7 +27583,7 @@
           <t>B | 730呎 (3房)
 $1605万
 $21,986/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -27623,7 +27591,7 @@
           <t>C | 714呎 (3房)
 $1634万
 $22,881/呎
-(26年-10月-03日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -27631,7 +27599,7 @@
           <t>D | 461呎 (2房)
 $870万
 $18,863/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -27639,7 +27607,7 @@
           <t>E | 460呎 (2房)
 $864万
 $18,772/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -27654,7 +27622,7 @@
           <t>A | 723呎 (3房)
 $1437万
 $19,878/呎
-(26年-09月-27日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -27662,7 +27630,7 @@
           <t>B | 730呎 (3房)
 $1448万
 $19,836/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -27670,7 +27638,7 @@
           <t>C | 714呎 (3房)
 $1486万
 $20,808/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -27678,7 +27646,7 @@
           <t>D | 461呎 (2房)
 $867万
 $18,807/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -27686,7 +27654,7 @@
           <t>E | 460呎 (2房)
 $861万
 $18,715/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -27701,7 +27669,7 @@
           <t>A | 723呎 (3房)
 $1420万
 $19,643/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -27709,7 +27677,7 @@
           <t>B | 730呎 (3房)
 $1567万
 $21,468/呎
-(26年-09月-27日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -27717,7 +27685,7 @@
           <t>C | 714呎 (3房)
 $1480万
 $20,725/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -27725,7 +27693,7 @@
           <t>D | 461呎 (2房)
 $885万
 $19,197/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -27733,7 +27701,7 @@
           <t>E | 460呎 (2房)
 $858万
 $18,661/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -27748,7 +27716,7 @@
           <t>A | 723呎 (3房)
 $1403万
 $19,411/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -27756,7 +27724,7 @@
           <t>B | 730呎 (3房)
 $1414万
 $19,368/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -27764,7 +27732,7 @@
           <t>C | 714呎 (3房)
 $1614万
 $22,608/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -27772,7 +27740,7 @@
           <t>D | 461呎 (2房)
 $862万
 $18,694/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -27780,7 +27748,7 @@
           <t>E | 460呎 (2房)
 $856万
 $18,604/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27763,7 @@
           <t>A | 723呎 (3房)
 $1403万
 $19,411/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -27803,7 +27771,7 @@
           <t>B | 730呎 (3房)
 $1414万
 $19,368/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -27811,7 +27779,7 @@
           <t>C | 714呎 (3房)
 $1509万
 $21,133/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -27819,7 +27787,7 @@
           <t>D | 461呎 (2房)
 $862万
 $18,694/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
@@ -27827,7 +27795,7 @@
           <t>E | 460呎 (2房)
 $856万
 $18,604/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -27842,7 +27810,7 @@
           <t>A | 723呎 (3房)
 $1392万
 $19,254/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -27850,7 +27818,7 @@
           <t>B | 730呎 (3房)
 $1536万
 $21,044/呎
-(26年-09月-27日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -27858,7 +27826,7 @@
           <t>C | 714呎 (3房)
 $1462万
 $20,478/呎
-(26年-10月-03日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -27866,7 +27834,7 @@
           <t>D | 461呎 (2房)
 $857万
 $18,581/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -27874,7 +27842,7 @@
           <t>E | 460呎 (2房)
 $851万
 $18,491/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -27889,7 +27857,7 @@
           <t>A | 723呎 (3房)
 $1519万
 $21,004/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -27897,7 +27865,7 @@
           <t>B | 730呎 (3房)
 $1397万
 $19,137/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -27905,7 +27873,7 @@
           <t>C | 714呎 (3房)
 $1595万
 $22,338/呎
-(26年-10月-03日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -27913,7 +27881,7 @@
           <t>D | 461呎 (2房)
 $854万
 $18,527/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -27921,7 +27889,7 @@
           <t>E | 460呎 (2房)
 $848万
 $18,435/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -27936,7 +27904,7 @@
           <t>A | 723呎 (3房)
 $1447万
 $20,011/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
@@ -27944,7 +27912,7 @@
           <t>B | 730呎 (3房)
 $1391万
 $19,060/呎
-(26年-09月-27日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -27952,7 +27920,7 @@
           <t>C | 714呎 (3房)
 $1450万
 $20,314/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -27960,7 +27928,7 @@
           <t>D | 461呎 (2房)
 $852万
 $18,471/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -27968,7 +27936,7 @@
           <t>E | 460呎 (2房)
 $846万
 $18,380/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -27983,7 +27951,7 @@
           <t>A | 723呎 (3房)
 $1506万
 $20,837/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
@@ -27991,7 +27959,7 @@
           <t>B | 730呎 (3房)
 $1386万
 $18,985/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -27999,7 +27967,7 @@
           <t>C | 714呎 (3房)
 $1445万
 $20,232/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -28007,7 +27975,7 @@
           <t>D | 461呎 (2房)
 $849万
 $18,416/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
@@ -28015,7 +27983,7 @@
           <t>E | 460呎 (2房)
 $923万
 $20,072/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -28030,7 +27998,7 @@
           <t>A | 723呎 (3房)
 $1370万
 $18,949/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
@@ -28038,7 +28006,7 @@
           <t>B | 730呎 (3房)
 $1512万
 $20,710/呎
-(26年-09月-27日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -28046,7 +28014,7 @@
           <t>C | 714呎 (3房)
 $1507万
 $21,111/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -28054,7 +28022,7 @@
           <t>D | 461呎 (2房)
 $846万
 $18,360/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F34" s="21" t="inlineStr">
@@ -28062,7 +28030,7 @@
           <t>E | 460呎 (2房)
 $840万
 $18,272/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -28077,7 +28045,7 @@
           <t>A | 723呎 (3房)
 $1364万
 $18,873/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
@@ -28085,7 +28053,7 @@
           <t>B | 730呎 (3房)
 $1375万
 $18,833/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="D35" s="21" t="inlineStr">
@@ -28093,7 +28061,7 @@
           <t>C | 714呎 (3房)
 $1433万
 $20,071/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
@@ -28101,7 +28069,7 @@
           <t>D | 461呎 (2房)
 $924万
 $20,048/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F35" s="21" t="inlineStr">
@@ -28109,7 +28077,7 @@
           <t>E | 460呎 (2房)
 $858万
 $18,650/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -28124,7 +28092,7 @@
           <t>A | 723呎 (3房)
 $1424万
 $19,692/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
@@ -28132,7 +28100,7 @@
           <t>B | 730呎 (3房)
 $1402万
 $19,203/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -28140,7 +28108,7 @@
           <t>C | 714呎 (3房)
 $1495万
 $20,943/呎
-(26年-10月-03日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
@@ -28148,7 +28116,7 @@
           <t>D | 461呎 (2房)
 $921万
 $19,987/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F36" s="21" t="inlineStr">
@@ -28156,7 +28124,7 @@
           <t>E | 460呎 (2房)
 $835万
 $18,161/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -28171,7 +28139,7 @@
           <t>A | 723呎 (3房)
 $1359万
 $18,797/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C37" s="21" t="inlineStr">
@@ -28179,7 +28147,7 @@
           <t>B | 730呎 (3房)
 $1369万
 $18,756/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
@@ -28187,7 +28155,7 @@
           <t>C | 714呎 (3房)
 $1427万
 $19,990/呎
-(26年-10月-03日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
@@ -28195,7 +28163,7 @@
           <t>D | 461呎 (2房)
 $921万
 $19,987/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F37" s="21" t="inlineStr">
@@ -28203,7 +28171,7 @@
           <t>E | 460呎 (2房)
 $835万
 $18,161/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -28218,7 +28186,7 @@
           <t>A | 723呎 (3房)
 $1348万
 $18,647/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
@@ -28226,7 +28194,7 @@
           <t>B | 730呎 (3房)
 $1358万
 $18,607/呎
-(26年-09月-27日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
@@ -28234,7 +28202,7 @@
           <t>C | 714呎 (3房)
 $1551万
 $21,718/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
@@ -28242,7 +28210,7 @@
           <t>D | 461呎 (2房)
 $836万
 $18,141/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F38" s="21" t="inlineStr">
@@ -28250,7 +28218,7 @@
           <t>E | 460呎 (2房)
 $910万
 $19,772/呎
-(26年-09月-27日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
     </row>
@@ -28265,7 +28233,7 @@
           <t>A | 723呎 (3房)
 $1471万
 $20,342/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C39" s="21" t="inlineStr">
@@ -28273,7 +28241,7 @@
           <t>B | 730呎 (3房)
 $1417万
 $19,415/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="D39" s="21" t="inlineStr">
@@ -28281,7 +28249,7 @@
           <t>C | 714呎 (3房)
 $1412万
 $19,772/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
@@ -28289,7 +28257,7 @@
           <t>D | 461呎 (2房)
 $913万
 $19,807/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F39" s="21" t="inlineStr">
@@ -28297,7 +28265,7 @@
           <t>E | 460呎 (2房)
 $828万
 $18,000/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -28312,7 +28280,7 @@
           <t>A | 723呎 (3房)
 $1337万
 $18,498/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
@@ -28320,7 +28288,7 @@
           <t>B | 730呎 (3房)
 $1348万
 $18,459/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
@@ -28328,7 +28296,7 @@
           <t>C | 714呎 (3房)
 $1407万
 $19,711/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
@@ -28336,7 +28304,7 @@
           <t>D | 461呎 (2房)
 $829万
 $17,978/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F40" s="21" t="inlineStr">
@@ -28344,7 +28312,7 @@
           <t>E | 460呎 (2房)
 $823万
 $17,889/呎
-(26年-09月-27日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
     </row>
@@ -28362,12 +28330,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C41" s="20" t="inlineStr">
+      <c r="C41" s="21" t="inlineStr">
         <is>
           <t>B | 686呎 (3房)
-招标单位
--
-(在售)</t>
+$1833万
+$26,726/呎
+(26年-10月-17日)</t>
         </is>
       </c>
       <c r="D41" s="21" t="inlineStr">
@@ -28375,7 +28343,7 @@
           <t>C | 676呎 (3房)
 $1780万
 $26,327/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E41" s="21" t="inlineStr">
@@ -28383,7 +28351,7 @@
           <t>D | 424呎 (2房)
 $1062万
 $25,050/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F41" s="21" t="inlineStr">
@@ -28391,7 +28359,7 @@
           <t>E | 423呎 (2房)
 $1020万
 $24,121/呎
-(26年-09月-29日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -28469,7 +28437,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -28479,7 +28447,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>172</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -28552,12 +28520,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>C | 322呎 (1房)
-招标单位
--
-(在售)</t>
+$801万
+$24,876/呎
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -28777,7 +28745,7 @@
           <t>C | 322呎 (1房)
 $699万
 $21,720/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -28824,7 +28792,7 @@
           <t>B | 447呎 (2房)
 $934万
 $20,884/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -28832,7 +28800,7 @@
           <t>C | 322呎 (1房)
 $662万
 $20,568/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -28840,7 +28808,7 @@
           <t>D | 306呎 (1房)
 $616万
 $20,134/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -28856,7 +28824,7 @@
           <t>F | 412呎 (2房)
 $850万
 $20,636/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -28934,7 +28902,7 @@
           <t>B | 447呎 (2房)
 $924万
 $20,678/呎
-(26年-10月-03日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -28942,7 +28910,7 @@
           <t>C | 322呎 (1房)
 $626万
 $19,441/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -28997,7 +28965,7 @@
           <t>C | 322呎 (1房)
 $682万
 $21,165/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -29036,7 +29004,7 @@
           <t>A | 628呎 (3房)
 $1452万
 $23,113/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -29044,7 +29012,7 @@
           <t>B | 447呎 (2房)
 $910万
 $20,351/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -29052,7 +29020,7 @@
           <t>C | 322呎 (1房)
 $680万
 $21,102/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -29060,7 +29028,7 @@
           <t>D | 306呎 (1房)
 $605万
 $19,758/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -29076,7 +29044,7 @@
           <t>F | 412呎 (2房)
 $798万
 $19,369/呎
-(26年-09月-27日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29059,7 @@
           <t>A | 628呎 (3房)
 $1437万
 $22,884/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -29099,7 +29067,7 @@
           <t>B | 447呎 (2房)
 $906万
 $20,271/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -29107,7 +29075,7 @@
           <t>C | 322呎 (1房)
 $677万
 $21,037/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -29115,7 +29083,7 @@
           <t>D | 306呎 (1房)
 $603万
 $19,696/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -29131,7 +29099,7 @@
           <t>F | 412呎 (2房)
 $790万
 $19,180/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29122,7 @@
           <t>B | 447呎 (2房)
 $902万
 $20,190/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -29162,7 +29130,7 @@
           <t>C | 322呎 (1房)
 $617万
 $19,152/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -29170,7 +29138,7 @@
           <t>D | 306呎 (1房)
 $601万
 $19,641/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -29186,7 +29154,7 @@
           <t>F | 412呎 (2房)
 $782万
 $18,988/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -29209,7 +29177,7 @@
           <t>B | 447呎 (2房)
 $984万
 $22,025/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -29225,7 +29193,7 @@
           <t>D | 306呎 (1房)
 $599万
 $19,578/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -29256,7 +29224,7 @@
           <t>A | 628呎 (3房)
 $1395万
 $22,210/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -29272,7 +29240,7 @@
           <t>C | 322呎 (1房)
 $613万
 $19,037/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -29296,7 +29264,7 @@
           <t>F | 412呎 (2房)
 $846万
 $20,529/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -29311,7 +29279,7 @@
           <t>A | 628呎 (3房)
 $1381万
 $21,990/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -29319,7 +29287,7 @@
           <t>B | 447呎 (2房)
 $892万
 $19,949/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -29327,7 +29295,7 @@
           <t>C | 322呎 (1房)
 $611万
 $18,978/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -29335,7 +29303,7 @@
           <t>D | 306呎 (1房)
 $596万
 $19,464/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -29351,7 +29319,7 @@
           <t>F | 412呎 (2房)
 $770万
 $18,687/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -29366,7 +29334,7 @@
           <t>A | 628呎 (3房)
 $1395万
 $22,220/呎
-(26年-09月-28日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -29374,7 +29342,7 @@
           <t>B | 447呎 (2房)
 $888万
 $19,870/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -29382,7 +29350,7 @@
           <t>C | 322呎 (1房)
 $609万
 $18,925/呎
-(26年-09月-27日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -29390,7 +29358,7 @@
           <t>D | 306呎 (1房)
 $594万
 $19,405/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -29406,7 +29374,7 @@
           <t>F | 412呎 (2房)
 $768万
 $18,631/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -29421,7 +29389,7 @@
           <t>A | 628呎 (3房)
 $1354万
 $21,557/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -29429,7 +29397,7 @@
           <t>B | 447呎 (2房)
 $888万
 $19,870/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -29437,7 +29405,7 @@
           <t>C | 322呎 (1房)
 $667万
 $20,727/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -29445,7 +29413,7 @@
           <t>D | 306呎 (1房)
 $594万
 $19,405/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -29461,7 +29429,7 @@
           <t>F | 412呎 (2房)
 $768万
 $18,631/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -29476,7 +29444,7 @@
           <t>A | 628呎 (3房)
 $1342万
 $21,369/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -29484,7 +29452,7 @@
           <t>B | 447呎 (2房)
 $881万
 $19,711/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -29492,7 +29460,7 @@
           <t>C | 322呎 (1房)
 $600万
 $18,621/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -29500,7 +29468,7 @@
           <t>D | 306呎 (1房)
 $590万
 $19,288/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -29516,7 +29484,7 @@
           <t>F | 412呎 (2房)
 $763万
 $18,519/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -29531,7 +29499,7 @@
           <t>A | 625呎 (3房)
 $1310万
 $20,954/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -29539,7 +29507,7 @@
           <t>B | 448呎 (2房)
 $958万
 $21,375/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -29555,7 +29523,7 @@
           <t>D | 307呎 (1房)
 $586万
 $19,098/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -29571,7 +29539,7 @@
           <t>F | 413呎 (2房)
 $757万
 $18,334/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -29586,7 +29554,7 @@
           <t>A | 625呎 (3房)
 $1306万
 $20,891/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -29594,7 +29562,7 @@
           <t>B | 448呎 (2房)
 $872万
 $19,455/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -29602,7 +29570,7 @@
           <t>C | 323呎 (1房)
 $594万
 $18,387/呎
-(26年-09月-27日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -29610,7 +29578,7 @@
           <t>D | 307呎 (1房)
 $584万
 $19,039/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -29626,7 +29594,7 @@
           <t>F | 413呎 (2房)
 $756万
 $18,298/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -29641,7 +29609,7 @@
           <t>A | 625呎 (3房)
 $1302万
 $20,829/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -29657,7 +29625,7 @@
           <t>C | 323呎 (1房)
 $592万
 $18,334/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -29665,7 +29633,7 @@
           <t>D | 307呎 (1房)
 $583万
 $18,984/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -29681,7 +29649,7 @@
           <t>F | 413呎 (2房)
 $754万
 $18,262/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -29704,7 +29672,7 @@
           <t>B | 448呎 (2房)
 $866万
 $19,339/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -29712,7 +29680,7 @@
           <t>C | 323呎 (1房)
 $605万
 $18,718/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -29720,7 +29688,7 @@
           <t>D | 307呎 (1房)
 $636万
 $20,726/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -29736,7 +29704,7 @@
           <t>F | 413呎 (2房)
 $753万
 $18,225/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -29751,7 +29719,7 @@
           <t>A | 625呎 (3房)
 $1294万
 $20,704/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -29759,7 +29727,7 @@
           <t>B | 448呎 (2房)
 $864万
 $19,281/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -29767,7 +29735,7 @@
           <t>C | 323呎 (1房)
 $617万
 $19,096/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -29775,7 +29743,7 @@
           <t>D | 307呎 (1房)
 $579万
 $18,866/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -29791,7 +29759,7 @@
           <t>F | 413呎 (2房)
 $823万
 $19,920/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -29806,7 +29774,7 @@
           <t>A | 625呎 (3房)
 $1321万
 $21,133/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -29814,7 +29782,7 @@
           <t>B | 448呎 (2房)
 $943万
 $21,054/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -29822,7 +29790,7 @@
           <t>C | 323呎 (1房)
 $643万
 $19,907/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -29830,7 +29798,7 @@
           <t>D | 307呎 (1房)
 $578万
 $18,811/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -29846,7 +29814,7 @@
           <t>F | 413呎 (2房)
 $750万
 $18,153/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -29861,7 +29829,7 @@
           <t>A | 625呎 (3房)
 $1290万
 $20,642/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -29869,7 +29837,7 @@
           <t>B | 448呎 (2房)
 $861万
 $19,223/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -29885,7 +29853,7 @@
           <t>D | 307呎 (1房)
 $578万
 $18,811/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -29901,7 +29869,7 @@
           <t>F | 413呎 (2房)
 $750万
 $18,153/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -29916,7 +29884,7 @@
           <t>A | 625呎 (3房)
 $1344万
 $21,496/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -29924,7 +29892,7 @@
           <t>B | 448呎 (2房)
 $856万
 $19,109/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -29932,7 +29900,7 @@
           <t>C | 323呎 (1房)
 $639万
 $19,796/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -29940,7 +29908,7 @@
           <t>D | 307呎 (1房)
 $629万
 $20,479/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -29956,7 +29924,7 @@
           <t>F | 413呎 (2房)
 $747万
 $18,080/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -29971,7 +29939,7 @@
           <t>A | 625呎 (3房)
 $1278万
 $20,456/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -29979,7 +29947,7 @@
           <t>B | 448呎 (2房)
 $854万
 $19,051/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -29987,7 +29955,7 @@
           <t>C | 323呎 (1房)
 $582万
 $18,022/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -29995,7 +29963,7 @@
           <t>D | 307呎 (1房)
 $572万
 $18,642/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -30011,7 +29979,7 @@
           <t>F | 413呎 (2房)
 $816万
 $19,768/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -30026,7 +29994,7 @@
           <t>A | 625呎 (3房)
 $1396万
 $22,338/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
@@ -30034,7 +30002,7 @@
           <t>B | 448呎 (2房)
 $851万
 $18,996/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -30042,7 +30010,7 @@
           <t>C | 323呎 (1房)
 $636万
 $19,681/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -30050,7 +30018,7 @@
           <t>D | 307呎 (1房)
 $571万
 $18,590/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -30066,7 +30034,7 @@
           <t>F | 413呎 (2房)
 $744万
 $18,007/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -30081,7 +30049,7 @@
           <t>A | 625呎 (3房)
 $1271万
 $20,334/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
@@ -30089,7 +30057,7 @@
           <t>B | 448呎 (2房)
 $869万
 $19,388/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -30097,7 +30065,7 @@
           <t>C | 323呎 (1房)
 $579万
 $17,916/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -30105,7 +30073,7 @@
           <t>D | 307呎 (1房)
 $569万
 $18,531/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -30121,7 +30089,7 @@
           <t>F | 413呎 (2房)
 $813万
 $19,685/呎
-(26年-09月-27日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
     </row>
@@ -30136,7 +30104,7 @@
           <t>A | 625呎 (3房)
 $1267万
 $20,274/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
@@ -30144,7 +30112,7 @@
           <t>B | 448呎 (2房)
 $846万
 $18,879/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -30152,7 +30120,7 @@
           <t>C | 323呎 (1房)
 $632万
 $19,567/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -30160,7 +30128,7 @@
           <t>D | 307呎 (1房)
 $567万
 $18,476/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -30176,7 +30144,7 @@
           <t>F | 413呎 (2房)
 $741万
 $17,937/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -30191,7 +30159,7 @@
           <t>A | 625呎 (3房)
 $1263万
 $20,211/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
@@ -30199,7 +30167,7 @@
           <t>B | 448呎 (2房)
 $884万
 $19,721/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D35" s="21" t="inlineStr">
@@ -30215,7 +30183,7 @@
           <t>D | 307呎 (1房)
 $566万
 $18,420/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -30231,7 +30199,7 @@
           <t>F | 413呎 (2房)
 $739万
 $17,898/呎
-(26年-09月-27日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
     </row>
@@ -30246,7 +30214,7 @@
           <t>A | 625呎 (3房)
 $1260万
 $20,152/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
@@ -30254,7 +30222,7 @@
           <t>B | 448呎 (2房)
 $841万
 $18,768/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -30262,7 +30230,7 @@
           <t>C | 323呎 (1房)
 $628万
 $19,455/呎
-(26年-09月-27日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
@@ -30270,7 +30238,7 @@
           <t>D | 307呎 (1房)
 $591万
 $19,238/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -30286,7 +30254,7 @@
           <t>F | 413呎 (2房)
 $738万
 $17,864/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -30301,7 +30269,7 @@
           <t>A | 625呎 (3房)
 $1260万
 $20,152/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C37" s="21" t="inlineStr">
@@ -30309,7 +30277,7 @@
           <t>B | 448呎 (2房)
 $841万
 $18,768/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
@@ -30317,7 +30285,7 @@
           <t>C | 323呎 (1房)
 $574万
 $17,765/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
@@ -30325,7 +30293,7 @@
           <t>D | 307呎 (1房)
 $618万
 $20,114/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -30341,7 +30309,7 @@
           <t>F | 413呎 (2房)
 $808万
 $19,567/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -30356,7 +30324,7 @@
           <t>A | 625呎 (3房)
 $1252万
 $20,030/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
@@ -30372,7 +30340,7 @@
           <t>C | 323呎 (1房)
 $625万
 $19,341/呎
-(26年-09月-27日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
@@ -30380,7 +30348,7 @@
           <t>D | 307呎 (1房)
 $555万
 $18,078/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
@@ -30396,7 +30364,7 @@
           <t>F | 413呎 (2房)
 $735万
 $17,794/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -30411,7 +30379,7 @@
           <t>A | 625呎 (3房)
 $1248万
 $19,971/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C39" s="21" t="inlineStr">
@@ -30419,7 +30387,7 @@
           <t>B | 448呎 (2房)
 $833万
 $18,598/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D39" s="21" t="inlineStr">
@@ -30427,7 +30395,7 @@
           <t>C | 323呎 (1房)
 $618万
 $19,149/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
@@ -30435,7 +30403,7 @@
           <t>D | 307呎 (1房)
 $550万
 $17,899/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F39" s="22" t="inlineStr">
@@ -30451,7 +30419,7 @@
           <t>F | 413呎 (2房)
 $724万
 $17,525/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -30466,7 +30434,7 @@
           <t>A | 625呎 (3房)
 $1244万
 $19,910/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
@@ -30474,7 +30442,7 @@
           <t>B | 448呎 (2房)
 $828万
 $18,487/呎
-(26年-10月-03日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
@@ -30482,7 +30450,7 @@
           <t>C | 323呎 (1房)
 $558万
 $17,263/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
@@ -30490,7 +30458,7 @@
           <t>D | 307呎 (1房)
 $543万
 $17,674/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
@@ -30506,7 +30474,7 @@
           <t>F | 413呎 (2房)
 $699万
 $16,930/呎
-(26年-09月-27日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
     </row>
@@ -30516,12 +30484,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B41" s="20" t="inlineStr">
+      <c r="B41" s="21" t="inlineStr">
         <is>
           <t>A | 588呎 (3房)
-招标单位
--
-(在售)</t>
+$1443万
+$24,541/呎
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
@@ -30529,7 +30497,7 @@
           <t>B | 409呎 (2房)
 $1001万
 $24,467/呎
-(26年-09月-29日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
@@ -30561,7 +30529,7 @@
           <t>F | 375呎 (2房)
 $855万
 $22,792/呎
-(26年-09月-27日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-西南九龙-叡璟II.xlsx
+++ b/files/九龙-西南九龙-叡璟II.xlsx
@@ -1370,7 +1370,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -13022,7 +13022,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13154,7 +13154,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13410,7 +13410,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13930,7 +13930,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -14062,7 +14062,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -14186,7 +14186,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14706,7 +14706,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14838,7 +14838,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14962,7 +14962,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -15226,7 +15226,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15614,7 +15614,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -16948,7 +16948,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17522,7 +17522,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17646,7 +17646,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -20748,7 +20748,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -26682,7 +26682,7 @@
           <t>A | 722呎 (3房)
 $1923万
 $26,629/呎
-(26年-10月-11日)</t>
+(26年-10月-29日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -26800,7 +26800,7 @@
           <t>D | 461呎 (2房)
 $970万
 $21,043/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -27011,7 +27011,7 @@
           <t>A | 722呎 (3房)
 $1798万
 $24,903/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -27066,7 +27066,7 @@
           <t>B | 730呎 (3房)
 $1723万
 $23,599/呎
-(26年-10月-07日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -27207,7 +27207,7 @@
           <t>B | 730呎 (3房)
 $1672万
 $22,904/呎
-(26年-10月-06日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -27442,7 +27442,7 @@
           <t>B | 730呎 (3房)
 $1630万
 $22,329/呎
-(26年-10月-06日)</t>
+(26年-10月-29日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -28533,7 +28533,7 @@
           <t>D | 306呎 (1房)
 $751万
 $24,549/呎
-(26年-10月-06日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -28572,7 +28572,7 @@
           <t>B | 447呎 (2房)
 $995万
 $22,251/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -28588,7 +28588,7 @@
           <t>D | 306呎 (1房)
 $715万
 $23,356/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -28604,7 +28604,7 @@
           <t>F | 412呎 (2房)
 $880万
 $21,347/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
     </row>
@@ -28627,7 +28627,7 @@
           <t>B | 447呎 (2房)
 $979万
 $21,902/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -28635,7 +28635,7 @@
           <t>C | 322呎 (1房)
 $725万
 $22,503/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -28643,7 +28643,7 @@
           <t>D | 306呎 (1房)
 $645万
 $21,072/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -28659,7 +28659,7 @@
           <t>F | 412呎 (2房)
 $869万
 $21,095/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
     </row>
@@ -28682,7 +28682,7 @@
           <t>B | 447呎 (2房)
 $952万
 $21,306/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -28690,7 +28690,7 @@
           <t>C | 322呎 (1房)
 $645万
 $20,031/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -28698,7 +28698,7 @@
           <t>D | 306呎 (1房)
 $658万
 $21,520/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -28714,7 +28714,7 @@
           <t>F | 412呎 (2房)
 $847万
 $20,561/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
     </row>
@@ -28737,7 +28737,7 @@
           <t>B | 447呎 (2房)
 $943万
 $21,094/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -28753,7 +28753,7 @@
           <t>D | 306呎 (1房)
 $622万
 $20,333/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -28769,7 +28769,7 @@
           <t>F | 412呎 (2房)
 $919万
 $22,296/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
     </row>
@@ -28847,7 +28847,7 @@
           <t>B | 447呎 (2房)
 $924万
 $20,678/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -28863,7 +28863,7 @@
           <t>D | 306呎 (1房)
 $610万
 $19,935/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -28879,7 +28879,7 @@
           <t>F | 412呎 (2房)
 $822万
 $19,956/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
     </row>
@@ -28918,7 +28918,7 @@
           <t>D | 306呎 (1房)
 $610万
 $19,935/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -28934,7 +28934,7 @@
           <t>F | 412呎 (2房)
 $814万
 $19,760/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
     </row>
@@ -28957,7 +28957,7 @@
           <t>B | 447呎 (2房)
 $1000万
 $22,380/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -28973,7 +28973,7 @@
           <t>D | 306呎 (1房)
 $606万
 $19,817/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -28989,7 +28989,7 @@
           <t>F | 412呎 (2房)
 $806万
 $19,563/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
     </row>
@@ -29114,7 +29114,7 @@
           <t>A | 628呎 (3房)
 $1423万
 $22,658/呎
-(26年-10月-08日)</t>
+(26年-10月-29日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -29169,7 +29169,7 @@
           <t>A | 628呎 (3房)
 $1409万
 $22,433/呎
-(26年-10月-06日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -29232,7 +29232,7 @@
           <t>B | 447呎 (2房)
 $895万
 $20,029/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -29248,7 +29248,7 @@
           <t>D | 306呎 (1房)
 $597万
 $19,523/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -29617,7 +29617,7 @@
           <t>B | 448呎 (2房)
 $869万
 $19,397/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -29664,7 +29664,7 @@
           <t>A | 625呎 (3房)
 $1298万
 $20,766/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
